--- a/tools/importer/reports/import-press-release.report.xlsx
+++ b/tools/importer/reports/import-press-release.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="878">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -37,28 +43,2610 @@
     <t>url</t>
   </si>
   <si>
+    <t>area-stampa/press-releases/2016/acalabrutinib-ema.report.json</t>
+  </si>
+  <si>
+    <t>["hero-press","download-press"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/acalabrutinib-ema</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>press-release</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:55:15.720Z</t>
+  </si>
+  <si>
+    <t>Acalabrutinib raccomandato in Europa per la designazione di Farmaco Orfano in tre indicazioni</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/acalabrutinib_EMA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/accordo-cilag.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/accordo-cilag</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:23:29.854Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca completa l’accordo con Cilag Gmbh International per i diritti su budesonide al di fuori degli Stati Uniti</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/accordo_Cilag.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/accordoaspen.report.json</t>
+  </si>
+  <si>
+    <t>["hero-press","download-press","table-press"]</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/accordoaspen</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:12:39.053Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca stipula un accordo di commercializzazione con Aspen per il portfolio di farmaci anestetici</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/accordoaspen.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/accordoolaparivconfmi.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/accordoolaparivconfmi</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:24:04.873Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca e Foundation Medicine danno il via a una collaborazione strategica per il test diagnostico abbinato per olaparib</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/accordoolaparivconFMI.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/acerta-pharma.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/acerta-pharma</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:24:39.741Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca completa la transazione per l’acquisizione della partecipazione azionaria di maggioranza in Acerta Pharma</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/acerta_pharma.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/allergan.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/allergan</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:25:14.736Z</t>
+  </si>
+  <si>
+    <t>MedImmune concede in licenza ad Allergan un farmaco potenziale per il trattamento delle malattie infiammatorie</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/allergan.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/aralez.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/aralez</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:55:50.738Z</t>
+  </si>
+  <si>
+    <t>Negli Stati Uniti, AstraZeneca stringe un accordo con Aralez per metoprololo succinato</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/aralez.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/astrazeneca-stipula-due-accordi-di-licenza-con-leo-pharmap-er-il-trattamento-delle-malattie-cutanee.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/astrazeneca-stipula-due-accordi-di-licenza-con-leo-pharmap-er-il-trattamento-delle-malattie-cutanee</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:56:27.030Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca stipula due accordi di licenza con Leo Pharma per il trattamento delle malattie cutanee</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/astraZeneca-stipula-due-accordi-di-licenza-con-leo-pharmap-er-il-trattamento-delle-malattie-cutanee.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/benralizumab-sirocco-calima.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/benralizumab-sirocco-calima</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:57:02.846Z</t>
+  </si>
+  <si>
+    <t>Risultati positivi per benralizumab nel suo programma di fase III per il trattamento dell’asma grave</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/benralizumab_sirocco_calima.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/benralizumabers.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/benralizumabers</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:25:48.877Z</t>
+  </si>
+  <si>
+    <t>Asma grave. Benralizumab dimostra risultati positivi in alcuni trial di fase III presentati al congresso ERS 2016</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/benralizumabERS.html</t>
+  </si>
+  <si>
     <t>area-stampa/press-releases/2016/caz-avi-chmp.report.json</t>
   </si>
   <si>
-    <t>["hero-press","download-press"]</t>
-  </si>
-  <si>
     <t>area-stampa/press-releases/2016/caz-avi-chmp</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>press-release</t>
-  </si>
-  <si>
-    <t>2026-04-04T15:40:21.792Z</t>
+    <t>2026-04-05T00:18:18.905Z</t>
   </si>
   <si>
     <t>Parere positivo del CHMP per ceftazidime-avibactam nell’UE per il trattamento delle infezioni batteriche gravi</t>
   </si>
   <si>
     <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/CAZ-AVI-CHMP.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/cediranib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/cediranib</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:26:24.642Z</t>
+  </si>
+  <si>
+    <t>Da AstraZeneca un aggiornamento sulla domanda di autorizzazione all’immissione in commercio di cediranib nell’Unione Europea</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/cediranib.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ceftazidime-avibactam-approvato-nell-unione-europea-per-il-trattamento-dei-pazienti-con-gravi-infezioni-batteriche.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ceftazidime-avibactam-approvato-nell-unione-europea-per-il-trattamento-dei-pazienti-con-gravi-infezioni-batteriche</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:26:59.106Z</t>
+  </si>
+  <si>
+    <t>Ceftazidime/avibactam approvato nell’Unione Europea per il trattamento dei pazienti con gravi infezioni batteriche</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/ceftazidime-avibactam-approvato-nell-unione-europea-per-il-trattamento-dei-pazienti-con-gravi-infezioni-batteriche.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ceftazidime-avibactam.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ceftazidime-avibactam</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:27:33.830Z</t>
+  </si>
+  <si>
+    <t>L’antibiotico ceftazidime-avibactam raggiunge gli endpoint primari nello studio di fase III per il trattamento della polmonite acquisita in ospedale</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/ceftazidime-avibactam.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/congressiscientifici.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/congressiscientifici</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:57:39.012Z</t>
+  </si>
+  <si>
+    <t>Oncologia: AstraZeneca protagonista nei principali congressi scientifici negli Stati Uniti ed in Europa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/congressiscientifici.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/consorzio-rcp2.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/consorzio-rcp2</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:58:13.380Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca e MedImmune istituiscono un consorzio per offrire nuovi trattamenti per la nefropatia cronica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/consorzio-RCP2.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/dapagliflozin.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/dapagliflozin</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:28:08.736Z</t>
+  </si>
+  <si>
+    <t>Dapagliflozin protagonista di due nuovi trial di fase IIIb per il trattamento dell’insufficienza renale cronica e dello scompenso cardiaco cronico</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/dapagliflozin.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/davidgoldstein.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/davidgoldstein</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:58:49.752Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca nomina David Goldstein come chief advisor per la sua iniziativa sulla genomica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/davidgoldstein.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumab-breakthroughtherapy.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumab-breakthroughtherapy</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:28:43.977Z</t>
+  </si>
+  <si>
+    <t>Durvalumab ha ottenuto la designazione di Breakthrough Therapy dalla FDA Americana per il trattamento del carcinoma uroteliale della vescica PD-L1-positivo</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/durvalumab-breakthroughTherapy.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumab.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumab</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:23:40.446Z</t>
+  </si>
+  <si>
+    <t>Accettata dalla FDA la prima domanda di licenza per durvalumab per il trattamento del tumore alla vescica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/durvalumab.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumabasco2016.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumabasco2016</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:00:00.211Z</t>
+  </si>
+  <si>
+    <t>ASCO 2016 – La monoterapia con durvalumab efficace nel tumore uroteliale della vescica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/durvalumabasco2016.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumabesmo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/durvalumabesmo</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:13:14.470Z</t>
+  </si>
+  <si>
+    <t>ESMO 2016: durvalumab mostra dati iniziali promettenti per il trattamento del tumore al polmone e del tumore testa collo</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/durvalumabesmo.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/eccmid-2016.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/eccmid-2016</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:18:52.323Z</t>
+  </si>
+  <si>
+    <t>Un’analisi aggregata di sette studi clinici dimostra l’efficacia consistente di ceftazidime-avibactam nel trattamento di batteri Gram-negativi multi resistenti</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/ECCMID-2016.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/elcc-osimertinib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/elcc-osimertinib</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:29:18.644Z</t>
+  </si>
+  <si>
+    <t>European Lung Cancer Conference 2016: AstraZeneca presenta dati positivi di follow-up su osimertinib nel tumore al polmone</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/elcc_osimertinib.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/euclid.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/euclid</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:29:53.726Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca pubblica i risultati principali dello studio EUCLID sull’utilizzo di ticagrelor nel trattamento dell’arteriopatia obliterante periferica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/euclid.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/exenatide.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/exenatide</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:30:29.875Z</t>
+  </si>
+  <si>
+    <t>Diabete. La combinazione di exenatide a rilascio prolungato e dapagliflozin in pazienti con Diabete di tipo 2 ha dimostrato benefici significativi in un trial di fase III.</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/exenatide.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fda-glicopirrolato.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fda-glicopirrolato</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:19:27.726Z</t>
+  </si>
+  <si>
+    <t>La FDA approva la combinazione di glicopirrolato e formoterolo fumarato per il trattamento dei pazienti con BPCO</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/FDA-glicopirrolato.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/felodipina.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/felodipina</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:31:03.815Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca stipula un contratto di licenza con China Medical System Holdings per un farmaco contro l’ipertensione</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/felodipina.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fulvestrant-esmo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fulvestrant-esmo</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:32:12.677Z</t>
+  </si>
+  <si>
+    <t>ESMO 2016: Fulvestrant dimostra benefici significativi nella sopravvivenza libera da progressione nel trattamento di prima linea per il tumore al seno in stadio avanzato</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/fulvestrant_esmo.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fulvestrant-falcon.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fulvestrant-falcon</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:20:03.059Z</t>
+  </si>
+  <si>
+    <t>Fulvestrant raggiunge l’endpoint primario nel trattamento di prima linea del tumore al seno avanzato o metastatico</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/Fulvestrant_FALCON.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fulvestrantesmo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/fulvestrantesmo</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:31:38.000Z</t>
+  </si>
+  <si>
+    <t>Congresso ESMO 2016: AstraZeneca presenta nuovi dati su fulvestrant per il trattamento del tumore al seno e un aggiornamento sulle proprie terapie in immuno-oncologia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/fulvestrantESMO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/incyte.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/incyte</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:32:47.867Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca e Incyte annunciano una nuova collaborazione per uno studio clinico sul tumore al polmone</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/incyte.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ironwwod.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ironwwod</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:33:23.787Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca stipula un contratto di licenza con Ironwood Pharmaceuticals per lesinurad negli Stati Uniti</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/ironwwod.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/lesinurad.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/lesinurad</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:00:35.079Z</t>
+  </si>
+  <si>
+    <t>Lesinurad approvato in Europa per il trattamento dei pazienti affetti da gotta</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/lesinurad.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/lesinurad1.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/lesinurad1</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:01:09.761Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca concede la licenza di lesinurad a Grünenthal GmbH in Europa e America Latina</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/lesinurad1.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/linee-guida-acc-aha-ticagrelor.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/linee-guida-acc-aha-ticagrelor</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:20:38.337Z</t>
+  </si>
+  <si>
+    <t>Ticagrelor raccomandato rispetto a clopidogrel nelle linee guida aggiornate dell’American College of Cardiology e dell’American Heart Association sulla Sindrome Coronarica Acuta</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/Linee-guida-ACC-AHA-ticagrelor.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/lynparza-breakthroughtherapy.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/lynparza-breakthroughtherapy</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:34:00.180Z</t>
+  </si>
+  <si>
+    <t>Olaparib ottiene la designazione di Breakthrough Therapy dalla FDA statunitense per il trattamento del tumore alla prostata metastatico resistente alla castrazione con mutazione dei geni BRCA1/2 o ATM</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/lynparza-breakthroughTherapy.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/medi551-orphan-drug.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/medi551-orphan-drug</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:21:12.292Z</t>
+  </si>
+  <si>
+    <t>Il farmaco di AstraZeneca in fase di sviluppo per la neuromielite ottica riceve la designazione di medicinale orfano dalla FDA</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/MEDI551_Orphan_Drug.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/medi8852-fda-fast-track.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/medi8852-fda-fast-track</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:21:47.283Z</t>
+  </si>
+  <si>
+    <t>Medimmune riceve la designazione Fast Track negli Stati Uniti per MEDI8852 per il trattamento dei pazienti ricoverati con influenza A</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/MEDI8852_FDA_Fast_Track.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/moderna-therapeutics.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/moderna-therapeutics</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:34:35.928Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca e Moderna Therapeutics annunciano una nuova collaborazione per lo sviluppo e la commercializzazione congiunta delle terapie immuno-oncologiche mRNA Therapeutics™</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/moderna_therapeutics.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/moventig-prostrakan.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/moventig-prostrakan</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:01:44.736Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca stipula un accordo con Prostrakan per i diritti su naloxegol in Europa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/moventig_Prostrakan.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparib-gold.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparib-gold</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:35:10.353Z</t>
+  </si>
+  <si>
+    <t>Pubblicati i risultati principali del trial GOLD su olaparib per il trattamento del tumore gastrico avanzato</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/olaparib_GOLD.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparib</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:21:01.401Z</t>
+  </si>
+  <si>
+    <t>Tumore ovarico: arriva in Italia la terapia contro la “mutazione Jolie”</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/olaparib.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparibasco2016.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparibasco2016</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:35:45.639Z</t>
+  </si>
+  <si>
+    <t>ASCO 2016 – Olaparib: gli ultimi dati suggeriscono un potenziale vantaggio in termini di sopravvivenza globale nelle pazienti con tumore ovarico platino-sensibile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/olaparibasco2016.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparibsolo2.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/olaparibsolo2</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:36:21.657Z</t>
+  </si>
+  <si>
+    <t>Nuove e ulteriori conferme per olaparib: il trial di fase III SOLO-2 dimostra vantaggi significativi in termini di sopravvivenza libera da progressione</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/olaparibsolo2.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/osimertinib-aura3.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/osimertinib-aura3</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:02:19.795Z</t>
+  </si>
+  <si>
+    <t>Tumore al polmone: osimertinib raggiunge l’endpoint primario nel trial di fase III AURA3</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/osimertinib_AURA3.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/osimertinib-ce.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/osimertinib-ce</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:13:48.744Z</t>
+  </si>
+  <si>
+    <t>Osimertinib approvato in Europa come primo trattamento di una nuova classe terapeutica per i pazienti con tumore al polmone non a piccole cellule metastatico positivo alla mutazione T790M dell’EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/osimertinib_CE.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/osimertinibasco2016.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/osimertinibasco2016</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:36:56.380Z</t>
+  </si>
+  <si>
+    <t>ASCO 2016 – Osimertinib mostra attività clinica nei pazienti con localizzazione leptomeningea del tumore al polmone</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/osimertinibasco2016.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/pfizer.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/pfizer</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:12:02.997Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca vende a Pfizer il proprio business di antibiotici a piccole molecole</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/Pfizer.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/plaiv-chmp.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/plaiv-chmp</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:54:05.583Z</t>
+  </si>
+  <si>
+    <t>Parere positivo del CHMP per il vaccino contro l’influenza pandemica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/PLAIV_CHMP.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ricerca-traslazionale.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ricerca-traslazionale</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:37:31.312Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca avvia una collaborazione con aziende del settore e il mondo accademico per creare un fondo per la ricerca traslazionale</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/ricerca_traslazionale.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ricercagenomica.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/ricercagenomica</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:38:06.450Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca: al via una nuova iniziativa genomica integrata per trasformare la scoperta e lo sviluppo di farmaci</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/ricercagenomica.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/risultati-socrates.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/risultati-socrates</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:38:43.004Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca pubblica i risultati principali del trial SOCRATES che ha studiato ticagrelor nella prevenzione secondaria dell’ictus</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/risultati_Socrates.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/saxa-dapa-chmp.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/saxa-dapa-chmp</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:22:21.632Z</t>
+  </si>
+  <si>
+    <t>Parere positivo del CHMP per la combinazione saxagliptin e dapagliflozin per il trattamento di pazienti adulti con diabete di tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/Saxa-dapa-CHMP.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/secretomics.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/secretomics</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:39:19.155Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca sfrutta le potenzialità del secretoma per lo sviluppo di farmaci biologici di nuova generazione in collaborazione con il nuovo Wallenberg Centre for Protein Research</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/secretomics.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/selumetinib-farmacoorfano.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/selumetinib-farmacoorfano</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:40:29.378Z</t>
+  </si>
+  <si>
+    <t>Selumetinib riceve la designazione di farmaco orfano negli Stati Uniti per la terapia adiuvante del tumore differenziato della tiroide</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/selumetinib_farmacoorfano.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/selumetinib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/selumetinib</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:39:53.625Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca pubblica un aggiornamento sul trial di fase III che ha valutato l’utilizzo di selumetinib nel trattamento del tumore al polmone non a piccole cellule (NSCLC)</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/selumetinib.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/takeda.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/takeda</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:02:55.320Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca completa l’acquisizione della divisione malattie respiratorie di Takeda</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/takeda.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/testbrca.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/testbrca</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:41:05.420Z</t>
+  </si>
+  <si>
+    <t>La lotta al tumore ovarico passa dal diritto al test genetico BRCA. Al via tre progetti nazionali: Società Scientifiche e Associazioni Pazienti dimostrano la necessità di garantire un accesso omogeneo al test in tutta Italia, per le pazienti e per la prevenzione dei famigliari. Appello forte alla Regione Lombardia: si chiede di “Scegliere di Sapere”.</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/testBRCA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/top-employer.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/top-employer</t>
+  </si>
+  <si>
+    <t>2026-04-05T02:54:40.743Z</t>
+  </si>
+  <si>
+    <t>Anche nel 2016 AstraZeneca ottiene la certificazione “Top Employers Italia”</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/Top_Employer.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/voluntis.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2016/voluntis</t>
+  </si>
+  <si>
+    <t>2026-04-05T00:22:55.363Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca e Voluntis in collaborazione con il National Cancer Institute Statunitense testano un’app di supporto negli studi sul cancro ovarico</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2016/Voluntis.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/aacr-oncologia.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/aacr-oncologia</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:13:06.347Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca condivide la sua solida early-science in oncologia con la comunità medica all’AACR 2017</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/AACR_oncologia.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/acalabrutinib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/acalabrutinib</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:56:16.383Z</t>
+  </si>
+  <si>
+    <t>Acalabrutinib di AstraZeneca approvato dall’FDA per i pazienti adulti con linfoma mantellare che hanno già ricevuto un trattamento</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/acalabrutinib.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/benralizumab-zonda.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/benralizumab-zonda</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:57:26.730Z</t>
+  </si>
+  <si>
+    <t>Il trial ZONDA di Fase III per benralizumab mostra la capacità di ridurre l’utilizzo di steroidi orali nei pazienti con asma grave</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/benralizumab_ZONDA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/benralizumab.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/benralizumab</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:56:51.628Z</t>
+  </si>
+  <si>
+    <t>Asma grave eosinofilico: parere positivo del CHMP per benralizumab di AstraZeneca</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/benralizumab.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/brodalumab.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/brodalumab</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:58:00.747Z</t>
+  </si>
+  <si>
+    <t>Brodalumab approvato dalla statunitense FDA per i pazienti adulti affetti da psoriasi a placche da moderata a grave</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/brodalumab.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/budesonide-formoterolo-spray.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/budesonide-formoterolo-spray</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:58:35.926Z</t>
+  </si>
+  <si>
+    <t>BPCO: disponibile in Italia la nuova formulazione spray di budesonide/formoterolo di AstraZeneca</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/budesonide_formoterolo_spray.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/cambridge-nuovasede.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/cambridge-nuovasede</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:46:16.292Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca raggiunge un obiettivo chiave con la posa dell'ultima pietra del nuovo centro R&amp;S globale e della sede centrale di Cambridge, Regno Unito</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Cambridge_nuovasede.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/circassia-patologierespiratorie.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/circassia-patologierespiratorie</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:46:51.979Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca e Circassia avviano una collaborazione strategica per le patologie respiratorie</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Circassia_patologierespiratorie.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/cvd-real-sglt2.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/cvd-real-sglt2</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:13:41.004Z</t>
+  </si>
+  <si>
+    <t>Lo studio CVD-Real presentato all'ACC ha dimostrato che gli inibitori dell' SGLT-2 riducono significativamente l'ospedalizzazione per scompenso cardiaco e la mortalità</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/CVD_Real_SGLT2.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/dapagliflozin-ada.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/dapagliflozin-ada</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:59:11.286Z</t>
+  </si>
+  <si>
+    <t>In occasione dell’ADA 2017, AstraZeneca ha presentato nuovi dati a sostegno del profilo di sicurezza e degli outcomes cardiovascolari real-world di dapagliflozin</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/dapagliflozin_ADA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/diabete-dapagliflozin-saxagliptin.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/diabete-dapagliflozin-saxagliptin</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:59:47.046Z</t>
+  </si>
+  <si>
+    <t>L'FDA approva le compresse di dapagliflozin/saxagliptin da assumere una volta al giorno per gli adulti con diabete di tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/diabete_dapagliflozin_saxagliptin.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-approvazionefda.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-approvazionefda</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:00:57.531Z</t>
+  </si>
+  <si>
+    <t>Durvalumab di AstraZeneca riceve approvazione accelerata dalla statunitense FDA per i pazienti con tumore della vescica in stadio avanzato precedentemente trattati con chemioterapia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/durvalumab_approvazioneFDA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-breakthrough-therapy-designation.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-breakthrough-therapy-designation</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:15:38.213Z</t>
+  </si>
+  <si>
+    <t>FDA: Breakthrough Therapy designation per durvalumab di AstraZeneca nel carcinoma polmonare non a piccole cellule localmente avanzato non operabile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/durvalumab_breakthrough therapy designation.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-ema.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-ema</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:47:27.346Z</t>
+  </si>
+  <si>
+    <t>L’EMA ha accettato la richiesta di autorizzazione all’immissione in commercio di durvalumab, prima immunoterapia per il carcinoma polmonare non a piccole cellule (NSCLC) localmente avanzato non resecabile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Durvalumab_EMA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-studiopacific.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/durvalumab-studiopacific</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:00:21.918Z</t>
+  </si>
+  <si>
+    <t>Durvalumab riduce significativamente il rischio di progressione della malattia o di morte nel trial di Fase III PACIFIC per il carcinoma polmonare non operabile in Stadio III</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/durvalumab_StudioPACIFIC.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/exenatide-studioexscel.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/exenatide-studioexscel</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:02:07.816Z</t>
+  </si>
+  <si>
+    <t>Lo studio EXSCEL con exenatide ha raggiunto l’endopoint primario di sicurezza in pazienti con diabete di Tipo-2 che presentano diversi tipi di rischio cardiovascolare</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/exenatide_studioEXSCEL.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/flaura-tumore-al-polmone1.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/flaura-tumore-al-polmone1</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:48:03.842Z</t>
+  </si>
+  <si>
+    <t>Osimertinib di AstraZeneca: potenziale nuovo standard terapeutico del carcinoma polmonare con EGFR mutato di prima linea</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/FLAURA_tumore_al_polmone1.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/globaldiabetespolicyforum.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/globaldiabetespolicyforum</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:48:38.557Z</t>
+  </si>
+  <si>
+    <t>A Roma il Global Diabetes Policy Forum: esperti nazionali e internazionali uniti per una corretta gestione del paziente</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/GlobalDiabetesPolicyForum.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/goserelin.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/goserelin</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:02:43.667Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca stipula un accordo con TerSera Therapeutics per Goserelin acetato negli USA e in Canada</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/goserelin.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/immunoncologia.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/immunoncologia</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:03:19.022Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca amplia le opportunità del programma di immuno-oncologia per il carcinoma polmonare di prima linea</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/immunoncologia.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/linfoma-mantellare.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/linfoma-mantellare</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:03:54.555Z</t>
+  </si>
+  <si>
+    <t>FDA: Breakthrough Therapy Designation e Priority Review per acalabrutinib di AstraZeneca per i pazienti con linfoma mantellare</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/linfoma_mantellare.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/medimmune-sanofipasteur-medi8897.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/medimmune-sanofipasteur-medi8897</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:49:14.967Z</t>
+  </si>
+  <si>
+    <t>MedImmune e Sanofi Pasteur formano un’alleanza per sviluppare e commercializzare il potenziale anticorpo di nuova generazione MEDI8897 contro il virus respiratorio sinciziale</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/MedImmune_SanofiPasteur_MEDI8897.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/neuromieliteottica.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/neuromieliteottica</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:49:50.759Z</t>
+  </si>
+  <si>
+    <t>Il farmaco di AstraZeneca studiato per il disturbo dello spettro della neuromielite ottica riceve la designazione di farmaco orfano in Europa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Neuromieliteottica.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-brca-solo2.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-brca-solo2</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:50:25.322Z</t>
+  </si>
+  <si>
+    <t>I dati di fase III dello Studio SOLO-2 su olaparib in terapia di mantenimento dimostrano un vantaggio in termini di sopravvivenza libera da progressione nel carcinoma ovarico con mutazione BRCA</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Olaparib_BRCA_SOLO2.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-carcinomamammario-olympiad.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-carcinomamammario-olympiad</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:51:34.256Z</t>
+  </si>
+  <si>
+    <t>Olaparib riduce significativamente il rischio di progressione della malattia o di morte nelle pazienti con carcinoma mammario metastatico BRCA mutato</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Olaparib_carcinomamammario_OlympiAD.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-olympiad.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-olympiad</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:51:00.469Z</t>
+  </si>
+  <si>
+    <t>Olaparib aumenta la sopravvivenza nelle pazienti affette da tumore al seno metastatico positivo alla mutazione BRCA</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Olaparib_OlympiAD.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-tumoreovarico-studiosolo2.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/olaparib-tumoreovarico-studiosolo2</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:52:10.152Z</t>
+  </si>
+  <si>
+    <t>La terapia di mantenimento con olaparib nelle donne con tumore ovarico BRCA mutato preserva la qualità di vita oltre ad aumentare la sopravvivenza libera da progressione</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Olaparib_tumoreovarico_studioSOLO2.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-btd.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-btd</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:52:45.176Z</t>
+  </si>
+  <si>
+    <t>Osimertinib ottiene dall’FDA la breakthrough therapy designation per il trattamento in prima linea dei pazienti affetti da carcinoma polmonare non a piccole cellule positivo alla mutazione dell’EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Osimertinib_BTD.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-cfda.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-cfda</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:05:06.166Z</t>
+  </si>
+  <si>
+    <t>Osimertinib approvato in Cina come primo trattamento per il carcinoma polmonare non a piccole cellule metastatico positivo alla mutazione T790M del recettore EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/osimertinib_cFDA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-fdausa.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-fdausa</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:04:29.851Z</t>
+  </si>
+  <si>
+    <t>Osimertinib riceve piena approvazione da parte della statunitense Food and Drug Administration (FDA)</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/osimertinib_FDAUSA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-rimborsabile.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-rimborsabile</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:05:39.900Z</t>
+  </si>
+  <si>
+    <t>Carcinoma polmonare: osimertinib ottiene la rimborsabilità</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/osimertinib_rimborsabile.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-tumorealpolmone-aura3.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/osimertinib-tumorealpolmone-aura3</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:06:14.934Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca presenta i dati di osimertinib nei pazienti con tumore al polmone positivo alla mutazione T790 dell'EGFR e metastasi al sistema nervoso centrale</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/osimertinib_tumorealpolmone_AURA3.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/pacific-tumore-al-polmone.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/pacific-tumore-al-polmone</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:53:21.823Z</t>
+  </si>
+  <si>
+    <t>Durvalumab di AstraZeneca, prima terapia immuno-oncologica a dimostrare una sopravvivenza libera da progressione superiore rispetto alla terapia standard per i pazienti affetti da carcinoma polmonare in stadio III localmente avanzato</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/PACIFIC_tumore_al_polmone.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/patient-advocacy-network.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/patient-advocacy-network</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:15:02.690Z</t>
+  </si>
+  <si>
+    <t>Associazioni pazienti sempre più preparate per un ruolo attivo nel governo del sistema sanitario: al via la terza edizione del Patient Advocacy Network</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Patient Advocacy Network.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/topemployers2017.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/topemployers2017</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:54:31.443Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca è Top Employer 2017</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/TopEmployers2017.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/zs-9-iperkaliemia.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/zs-9-iperkaliemia</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:55:07.201Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca riceve una Complete Response Letter dalla FDA per ZS-9 per il trattamento dell’iperkaliemia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/ZS-9_iperkaliemia.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/zs9-iperkaliemia-zspharma.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2017/zs9-iperkaliemia-zspharma</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:55:41.189Z</t>
+  </si>
+  <si>
+    <t>ZS-9 riceve il parere positivo del CHMP per il trattamento dell’iperkaliemia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/ZS9_iperkaliemia_ZSPharma.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/OLAPARIB_OVAIO_SOLOI_APPROVAZIONEEU.html.report.json</t>
+  </si>
+  <si>
+    <t>page.evaluate: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.evaluate: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:270:16)
+    at async main (/home/node/.excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:457:22)</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/OLAPARIB_OVAIO_SOLOI_APPROVAZIONEEU.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:34:09.778Z</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_OVAIO_SOLOI_APPROVAZIONEEU.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/OLAPARIB_PROFOUND_ESMO.html.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/OLAPARIB_PROFOUND_ESMO.html</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:34:09.781Z</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_PROFOUND_ESMO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/aa.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/aa</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:06:48.808Z</t>
+  </si>
+  <si>
+    <t>Lo studio di fase III THEMIS raggiunge il suo endpoint primario e conferma che ticagrelor riduce gli eventi cardiovascolari in pazienti affetti da diabete e malattia coronarica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/AA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-elevatetn-ash.report.json</t>
+  </si>
+  <si>
+    <t>["hero-press","download-press","table-press","table-press"]</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-elevatetn-ash</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:07:25.020Z</t>
+  </si>
+  <si>
+    <t>Leucemia linfatica cronica: acalabrutinib migliora significativamente il tempo libero da progressione o morte nei pazienti non precedentemente trattati</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ACALABRUTINIB_ELEVATETN_ASH.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-llc-approvazioneeu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-llc-approvazioneeu</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:08:00.717Z</t>
+  </si>
+  <si>
+    <t>Leucemia linfatica cronica: acalabrutinib è approvato in Europa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ACALABRUTINIB_LLC_APPROVAZIONEEU.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-llc-ascend.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-llc-ascend</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:08:36.611Z</t>
+  </si>
+  <si>
+    <t>Leucemia linfatica cronica: acalabrutinib migliora significativamente il tempo libero da progressione nei pazienti recidivanti o refrattari</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ACALABRUTINIB_LLC_ASCEND.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-llc-eha.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/acalabrutinib-llc-eha</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:09:11.480Z</t>
+  </si>
+  <si>
+    <t>Leucemia linfatica cronica: dimostrata l’efficacia e la tollerabilità a lungo termine di acalabrutinib</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ACALABRUTINIB_LLC_EHA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/aha-2018.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/aha-2018</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:09:46.321Z</t>
+  </si>
+  <si>
+    <t>Dapagliflozin riduce significativamente le ospedalizzazioni dovute a scompenso cardiaco o morte cardiovascolare in una vasta popolazione di pazienti affetti da diabete di tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/AHA_2018.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/aha-20181.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/aha-20181</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:10:20.326Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca è Top Employers Italia e Top Employers Europe 2019</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/AHA_20181.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-covid-19.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-covid-19</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:10:55.644Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca a supporto di medici e personale sanitario in prima linea nell’emergenza COVID-19, oggi e domani</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ASTRAZENECA_COVID-19.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-top-employers-2020.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-top-employers-2020</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:12:06.823Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca è Top Employers Italia e Top Employers Europe 2020</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ASTRAZENECA_TOP_EMPLOYERS_2020.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-topemployer2021.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-topemployer2021</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:11:31.290Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca è Top Employers Italia e Top Employers Europe 2021</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ASTRAZENECA_TOPEMPLOYER2021.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-vaccino-covid-19.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-vaccino-covid-19</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:12:42.147Z</t>
+  </si>
+  <si>
+    <t>Il vaccino AZD1222 per il COVID-19 ha prodotto importanti risposte immunitarie su tutti i partecipanti dello studio clinico di fase I/II</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ASTRAZENECA_VACCINO_COVID-19.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-vaccino-covid19.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/astrazeneca-vaccino-covid19</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:13:17.267Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca fornirà ai Paesi europei fino a 400 milioni di dosi del vaccino della Oxford University</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ASTRAZENECA_VACCINO_COVID19.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumab-bora-ers.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumab-bora-ers</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:15:39.705Z</t>
+  </si>
+  <si>
+    <t>Asma grave eosinofilico. Benralizumab, nello studio di fase III BORA, dimostra un profilo di sicurezza ed efficacia mantenuto nel lungo termine</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Benralizumab_BORA_ERS.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumab-chmp-autosomministrazione.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumab-chmp-autosomministrazione</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:13:52.388Z</t>
+  </si>
+  <si>
+    <t>Asma grave eosinofilico - Parere positivo del CHMP per il trattamento tramite auto-somministrazione di benralizumab e per l’utilizzo del nuovo dispositivo auto-iniettore pre-riempito monouso</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/BENRALIZUMAB_CHMP_AUTOSOMMINISTRAZIONE.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumab-ponente.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumab-ponente</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:14:27.518Z</t>
+  </si>
+  <si>
+    <t>ASMA GRAVE EOSINOFILICO – Dati dello studio di fase IIIb PONENTE mostrano che benralizumab elimina la necessità di ricorrere ai corticosteroidi orali nella maggior parte dei pazienti asmatici gravi</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/BENRALIZUMAB_PONENTE.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumabema.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/benralizumabema</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:17:59.145Z</t>
+  </si>
+  <si>
+    <t>Approvazione EMA per benralizumab di AstraZeneca nel trattamento dell’asma grave eosinofilico</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/benralizumabEMA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/budesonide-glicopirronio-formoterolo-ethos-bpco.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/budesonide-glicopirronio-formoterolo-ethos-bpco</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:15:03.578Z</t>
+  </si>
+  <si>
+    <t>Lo studio di Fase III ETHOS dimostra che la triplice terapia budesonide-glicopirronio-formoterolo fumarato riduce significativamente il tasso di riacutizzazioni moderate o severe in pazienti affetti da BPCO</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/BUDESONIDE-GLICOPIRRONIO-FORMOTEROLO_ETHOS_BPCO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/campagnaioscelgodisapere.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/campagnaioscelgodisapere</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:14:24.606Z</t>
+  </si>
+  <si>
+    <t>Seconda edizione di “Io scelgo di sapere”, la campagna di informazione sul tumore ovarico e ereditario e sul test genetico BRCA</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/campagnaioscelgodisapere.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-chmp-declare-cvdata.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-chmp-declare-cvdata</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:16:14.597Z</t>
+  </si>
+  <si>
+    <t>Diabete di tipo 2 – Parere positivo del CHMP per l'aggiornamento delle indicazioni di dapagliflozin: inclusi i dati di outcome cardio-renali dello studio DECLARE-TIMI 58</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DAPAGLIFLOZIN_CHMP_DECLARE_CVDATA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-dapa-ckd-esc.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-dapa-ckd-esc</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:16:50.174Z</t>
+  </si>
+  <si>
+    <t>Studio di Fase III DAPA-CKD: dapagliflozin ha dimostrato una riduzione senza precedenti del rischio di insufficienza renale e di morte per causa cardiovascolare o renale in pazienti affetti da malattia renale cronica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DAPAGLIFLOZIN_DAPA-CKD_ESC.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-dapa-hf-esc2019.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-dapa-hf-esc2019</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:17:25.038Z</t>
+  </si>
+  <si>
+    <t>Presentati a ESC 2019 i risultati dello studio di FASE III DAPA-HF che hanno mostrato come dapagliflozin abbia significativamente ridotto l’incidenza di morte per causa cardiovascolare e il peggioramento dello scompenso cardiaco</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DAPAGLIFLOZIN_DAPA-HF_ESC2019.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-dapackd-acc.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-dapackd-acc</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:18:00.550Z</t>
+  </si>
+  <si>
+    <t>Malattia renale cronica - Studio di Fase III DAPA-CKD interrotto in anticipo per conclamata efficacia di dapaglifozin sui pazienti</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DAPAGLIFLOZIN_DAPACKD_ACC.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-declare-renaldata.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-declare-renaldata</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:18:34.992Z</t>
+  </si>
+  <si>
+    <t>Lo studio di dapagliflozin ha mostrato la riduzione della progressione della malattia renale o della morte renale nei pazienti con diabete di tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DAPAGLIFLOZIN_DECLARE_renaldata.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-hf-approvazioneeu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapagliflozin-hf-approvazioneeu</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:19:09.267Z</t>
+  </si>
+  <si>
+    <t>Dapagliflozin approvato in Europa per il trattamento dello scompenso cardiaco</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DAPAGLIFLOZIN_HF_APPROVAZIONEEU.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapaglifozin-declare-top-line.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/dapaglifozin-declare-top-line</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:16:13.436Z</t>
+  </si>
+  <si>
+    <t>Dapagliflozin ha ottenuto risultati positivi nello studio di fase III DECLARE-TIMI 58, un ampio studio condotto sugli outcomes cardiovascolari che ha coinvolto 17.000 pazienti con diabete di tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Dapaglifozin__DECLARE_top_line.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/declaresottoanalisi.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/declaresottoanalisi</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:19:43.948Z</t>
+  </si>
+  <si>
+    <t>Risultati positivi dalla prime sotto-analisi dello studio di Fase III DECLARE-TIMI 58.</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DECLAREsottoanalisi.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-caspian-iaslc.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-caspian-iaslc</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:20:20.256Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone: durvalumab dimostra un significativo beneficio in termini di sopravvivenza e un miglioramento nel numero e nella durata delle risposte nel trattamento del carcinoma a piccole cellule in stadio avanzato</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DURVALUMAB_CASPIAN_IASLC.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-caspian-sclc-asco.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-caspian-sclc-asco</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:20:55.791Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone a piccole cellule. Durvalumab conferma un beneficio sostenuto di sopravvivenza globale quale trattamento di prima linea dei pazienti affetti da malattia estesa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DURVALUMAB_CASPIAN_SCLC_ASCO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-ok-ue-sclc.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-ok-ue-sclc</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:21:30.157Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone a piccole cellule - Ok della Commissione Europea per durvalumab nel trattamento della malattia estesa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DURVALUMAB_OK_UE_SCLC.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-pacific-esmo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-pacific-esmo</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:22:04.753Z</t>
+  </si>
+  <si>
+    <t>Carcinoma polmonare non a piccole cellule in stadio III non resecabile - Durvalumab mostra un beneficio di sopravvivenza a 4 anni senza precedenti per i pazienti in questo setting, per i quali si prospetta una possibilità di guarigione</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DURVALUMAB_PACIFIC_ESMO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-parerepositivochmp.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-parerepositivochmp</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:23:50.737Z</t>
+  </si>
+  <si>
+    <t>Parere positivo del CHMP per durvalumab nel carcinoma polmonare non a piccole cellule (NSCLC) localmente avanzato, non resecabile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Durvalumab_parerepositivoCHMP.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-tumorepolmone.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab-tumorepolmone</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:22:39.325Z</t>
+  </si>
+  <si>
+    <t>Durvalumab, unica immunoterapia con sopravvivenza globale a tre anni nel tumore del polmone non a piccole cellule in stadio III non operabile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/DURVALUMAB_TumorePolmone.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumab</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:18:34.429Z</t>
+  </si>
+  <si>
+    <t>FDA approva durvalumab per il trattamento del tumore al polmone non a piccole cellule al III Stadio non resecabile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/durvalumab.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumabpacificos.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/durvalumabpacificos</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:15:35.100Z</t>
+  </si>
+  <si>
+    <t>Durvalumab migliora significativamente la sopravvivenza globale nei pazienti con carcinoma polmonare non a piccole cellule in stadio III non operabile che hanno ancora possibilità di guarigione</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/durvalumabPACIFICOS.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/hlr-flaura-os.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/hlr-flaura-os</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:24:25.055Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone: osimertinib in prima linea migliora significativamente la sopravvivenza globale</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/HLR_FLAURA_OS.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/lung-ambition-alliance.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/lung-ambition-alliance</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:24:59.751Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone: nasce la Lung Ambition Alliance. L’obiettivo è raddoppiare la sopravvivenza a 5 anni entro il 2025</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/LUNG_AMBITION_ALLIANCE.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-chiara-gargiulo-vp-ria.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-chiara-gargiulo-vp-ria</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:29:36.334Z</t>
+  </si>
+  <si>
+    <t>Chiara Gargiulo è il nuovo Vice President della Business Unit Respiratory, Inflammation e Autoimmunity di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Nomina_Chiara_Gargiulo_VP_RIA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-driol-hr.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-driol-hr</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:25:34.731Z</t>
+  </si>
+  <si>
+    <t>Tamara Driol alla Direzione delle Risorse Umane di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOMINA_DRIOL_HR.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-mirkomerletti.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-mirkomerletti</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:26:09.238Z</t>
+  </si>
+  <si>
+    <t>Mirko Merletti nuovo Vice President della Business Unit Oncology di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOMINA_MIRKOMERLETTI.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-oliveros-medicalhead.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-oliveros-medicalhead</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:26:43.467Z</t>
+  </si>
+  <si>
+    <t>Constanza Oliveros nuovo Direttore Medico di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOMINA_OLIVEROS_MEDICALHEAD.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-scott-pescatore-vp-obu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/nomina-scott-pescatore-vp-obu</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:30:12.750Z</t>
+  </si>
+  <si>
+    <t>Scott Pescatore nuovo Vice President della Business Unit Oncology di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Nomina_Scott_Pescatore_VP_OBU.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/notastampa-dati-inglesi-rwe.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/notastampa-dati-inglesi-rwe</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:28:27.912Z</t>
+  </si>
+  <si>
+    <t>Studio inglese su dati di real world evidence (RWE) conferma l’efficacia del vaccino AstraZeneca nel prevenire tutti i livelli di gravità della malattia negli over 70</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOTASTAMPA_DATI_INGLESI_RWE.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/notastampaconsegnevaccino.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/notastampaconsegnevaccino</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:27:17.821Z</t>
+  </si>
+  <si>
+    <t>Dichiarazione di AstraZeneca in merito al ritardo delle consegne</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOTASTAMPACONSEGNEVACCINO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/notastampaestraneitavenditamercatiparalleli.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/notastampaestraneitavenditamercatiparalleli</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:27:52.378Z</t>
+  </si>
+  <si>
+    <t>Dichiarazione di AstraZeneca in merito all'estraneità alla vendita del vaccino su mercati paralleli</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOTASTAMPAESTRANEITAVENDITAMERCATIPARALLELI.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/novelstart.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/novelstart</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:29:02.491Z</t>
+  </si>
+  <si>
+    <t>Asma lieve - Nuovi dati mostrano l’efficacia della combinazione budesonide/formoterolo nella riduzione degli attacchi di asma lieve rispetto alla terapia comunemente più utilizzata</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/NOVELSTART.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-ovaio-soloi-approvazioneeu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-ovaio-soloi-approvazioneeu</t>
+  </si>
+  <si>
+    <t>2026-04-05T21:30:47.953Z</t>
+  </si>
+  <si>
+    <t>Carcinoma ovarico avanzato: olaparib approvato in Europa per il trattamento in prima linea delle pazienti con mutazione BRCA</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-paola-esmo2019.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-paola-esmo2019</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:33:40.254Z</t>
+  </si>
+  <si>
+    <t>Olaparib in associazione a bevacizumab aumenta significativamente il tempo libero da progressione nel trattamento di prima linea del tumore ovarico avanzato di nuova diagnosi</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_PAOLA_ESMO2019.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-paolai-approvazioneeu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-paolai-approvazioneeu</t>
+  </si>
+  <si>
+    <t>2026-04-05T20:33:04.874Z</t>
+  </si>
+  <si>
+    <t>Carcinoma ovarico avanzato: ok della Commissione Europea per olaparib in combinazione con bevacizumab per il trattamento di mantenimento in prima linea delle pazienti HRD-positive</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_PAOLAI_APPROVAZIONEEU.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-profound-esmo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-profound-esmo</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:21:20.673Z</t>
+  </si>
+  <si>
+    <t>Tumore della prostata: olaparib riduce il rischio di morte del 31% nei pazienti con malattia metastatica resistente alla castrazione e mutazione BRCA1/2 o ATM</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-profound-prostata-esmo2019.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-profound-prostata-esmo2019</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:21:57.088Z</t>
+  </si>
+  <si>
+    <t>Olaparib ha più che raddoppiato la sopravvivenza libera da progressione radiografica in pazienti con tumore della prostata metastatico resistente alla castrazione con mutazione BRCA1/2 o ATM (7,4 mesi rispetto a 3,6 dello standard di cura)</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_PROFOUND_PROSTATA_ESMO2019.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-profund-approvazioneeu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-profund-approvazioneeu</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:09:10.698Z</t>
+  </si>
+  <si>
+    <t>Tumore della prostata: ok della Commissione Europea per olaparib nel trattamento della malattia metastatica resistente alla castrazione con mutazione BRCA1/2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_PROFUND_APPROVAZIONEEU.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-psp-az-msd.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-psp-az-msd</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:09:44.928Z</t>
+  </si>
+  <si>
+    <t>Tumore dell’ovaio: dalla diagnosi al follow up, al via il programma CORE: Carcinoma Ovarico REmote Care per il supporto a domicilio delle pazienti durante l’emergenza covid-19 e oltre</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_PSP_AZ-MSD.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-seno-ovaio-rimborsabilita.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-seno-ovaio-rimborsabilita</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:10:20.668Z</t>
+  </si>
+  <si>
+    <t>Tumori del seno e dell’ovaio: svolta nel trattamento delle forme legate alla mutazione del gene BRCA. Olaparib da oggi disponibile nelle due neoplasie</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_SENO_OVAIO_RIMBORSABILITA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-solo-1-esmo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-solo-1-esmo</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:22:31.144Z</t>
+  </si>
+  <si>
+    <t>Carcinoma ovarico avanzato: olaparib in prima linea ritarda di oltre 4 anni e mezzo la progressione della malattia per le pazienti con mutazione BRCA</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_SOLO-1_ESMO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-tumorepancreas.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/olaparib-tumorepancreas</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:10:54.964Z</t>
+  </si>
+  <si>
+    <t>Tumore del pancreas: “Olaparib ha quasi raddoppiato il tempo di sopravvivenza senza progressione della malattia nei pazienti BRCA mutati”</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OLAPARIB_TumorePancreas.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-eu.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-eu</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:16:47.598Z</t>
+  </si>
+  <si>
+    <t>Approvazione europea per osimertinib in prima linea per i pazienti affetti da carcinoma polmonare non a piccole cellule (NSCLC) con mutazione di EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Osimertinib_Eu.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-flaura-esmo2019.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-flaura-esmo2019</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:16:20.900Z</t>
+  </si>
+  <si>
+    <t>Osimertinib: l'unico EGFR TKI ad aver dimostrato una sopravvivenza mediana superiore a 3 anni</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OSIMERTINIB_FLAURA_ESMO2019.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-nsclc-adaura-asco.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-nsclc-adaura-asco</t>
+  </si>
+  <si>
+    <t>2026-04-05T13:23:06.326Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone non a piccole cellule: osimertinib dimostra un risultato senza precedenti come terapia adiuvante in pazienti in stadio IB-IIIA positivi alla mutazione di EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OSIMERTINIB_NSCLC_ADAURA_ASCO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-rimborsabilita-1linea.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-rimborsabilita-1linea</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:11:28.625Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone non a piccole cellule avanzato: osimertinib disponibile in Italia per il trattamento in prima linea dei pazienti con mutazione di EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/OSIMERTINIB_RIMBORSABILITA_1LINEA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-tumorealpolmone-aura3.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/osimertinib-tumorealpolmone-aura3</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:19:11.359Z</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/osimertinib_tumorealpolmone_AURA3.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/pacific-os-wclc.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/pacific-os-wclc</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:12:37.248Z</t>
+  </si>
+  <si>
+    <t>Durvalumab è la prima immunoterapia che dimostra un beneficio significativo in sopravvivenza globale nel tumore del polmone in stadio III, non resecabile</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/PACIFIC_OS_WCLC.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/patientadvocacynetwork.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/patientadvocacynetwork</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:16:55.675Z</t>
+  </si>
+  <si>
+    <t>A Roma la quinta edizione del Patient Advocacy Network, organizzato da ALTEMS-Università Cattolica</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/PATIENTADVOCACYNETWORK.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/patientadvocacynetwork2018.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/patientadvocacynetwork2018</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:16:46.252Z</t>
+  </si>
+  <si>
+    <t>Associazioni di pazienti sempre più preparate e coinvolte nel governo del sistema sanitario: al via la quarta edizione del Patient Advocacy Network</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/patientadvocacynetwork2018.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/pennabenralizumab-disponibilitaitalia.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/pennabenralizumab-disponibilitaitalia</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:13:13.708Z</t>
+  </si>
+  <si>
+    <t>Asma grave eosinofilico - Approvata e disponibile in Italia la ‘penna’ per l’autosomministrazione di benralizumab</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/PENNABENRALIZUMAB_DISPONIBILITAITALIA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/senometastatico.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/senometastatico</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:32:46.395Z</t>
+  </si>
+  <si>
+    <t>Tumore alla mammella: ok della Commissione Europea per olaparip nella malattia avanzata HER2-negativa con mutazione BRCA</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/SENOMETASTATICO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/solo1-esmo2018.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/solo1-esmo2018</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:17:30.795Z</t>
+  </si>
+  <si>
+    <t>Carcinoma ovarico: olaparib in prima linea riduce il rischio di progressione o morte del 70%</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/SOLO1_ESMO2018.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/solo1-olaparib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/solo1-olaparib</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:17:23.081Z</t>
+  </si>
+  <si>
+    <t>Carcinoma ovarico: olaparib in prima linea ritarda in modo significativo la progressione della malattia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/Solo1_olaparib.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/studiocvdreal.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/studiocvdreal</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:20:31.830Z</t>
+  </si>
+  <si>
+    <t>Nuovi dati dallo studio CVD-REAL su pazienti con diabete di tipo 2 a conferma dei benefici cardiovascolari associati all’uso degli inibitori SGLT-2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/studiocvdreal.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/ticagrelor-themis-esc2019.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/ticagrelor-themis-esc2019</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:13:49.140Z</t>
+  </si>
+  <si>
+    <t>ESC 2019 - Lo studio di fase III THEMIS ha confermato che ticagrelor riduce il rischio di eventi cardiovascolari nei pazienti affetti da malattia coronarica e diabete di tipo 2</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/TICAGRELOR_THEMIS_ESC2019.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/ticagrelor.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/ticagrelor</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:21:06.840Z</t>
+  </si>
+  <si>
+    <t>Ticagrelor 60 mg riduce significativamente gli eventi cardiovascolari e la mortalità oltre l’anno nei pazienti che hanno avuto un attacco cardiaco e che presentano coronaropatia multivasale</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/ticagrelor.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/topemployers2017.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/topemployers2017</t>
+  </si>
+  <si>
+    <t>2026-04-05T03:18:41.533Z</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/TopEmployers2017.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/topemployers2018.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/topemployers2018</t>
+  </si>
+  <si>
+    <t>2026-04-06T04:21:40.796Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca è Top Employers Italia e Top Employers Europe 2018</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/topemployers2018.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/trialsygma.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2018/trialsygma</t>
+  </si>
+  <si>
+    <t>2026-04-05T01:18:29.791Z</t>
+  </si>
+  <si>
+    <t>Il New England Journal of Medicine ha pubblicato i risultati di due studi di budesonide/formoterolo via turbohaler® come terapia anti-infiammatoria al bisogno per il trattamento dell’asma lieve</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/trialsygma.html</t>
   </si>
 </sst>
 </file>
@@ -447,18 +3035,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="1" max="5" width="50" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,35 +3069,5551 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" t="s">
+        <v>88</v>
+      </c>
+      <c r="J16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I20" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" t="s">
+        <v>118</v>
+      </c>
+      <c r="J22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I23" t="s">
+        <v>123</v>
+      </c>
+      <c r="J23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" t="s">
+        <v>133</v>
+      </c>
+      <c r="J25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" t="s">
+        <v>138</v>
+      </c>
+      <c r="J26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" t="s">
+        <v>143</v>
+      </c>
+      <c r="J27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>147</v>
+      </c>
+      <c r="I28" t="s">
+        <v>148</v>
+      </c>
+      <c r="J28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s">
+        <v>152</v>
+      </c>
+      <c r="I29" t="s">
+        <v>153</v>
+      </c>
+      <c r="J29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>157</v>
+      </c>
+      <c r="I30" t="s">
+        <v>158</v>
+      </c>
+      <c r="J30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>162</v>
+      </c>
+      <c r="I31" t="s">
+        <v>163</v>
+      </c>
+      <c r="J31" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s">
+        <v>172</v>
+      </c>
+      <c r="I33" t="s">
+        <v>173</v>
+      </c>
+      <c r="J33" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" t="s">
+        <v>178</v>
+      </c>
+      <c r="J34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s">
+        <v>182</v>
+      </c>
+      <c r="I35" t="s">
+        <v>183</v>
+      </c>
+      <c r="J35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s">
+        <v>187</v>
+      </c>
+      <c r="I36" t="s">
+        <v>188</v>
+      </c>
+      <c r="J36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>191</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s">
+        <v>192</v>
+      </c>
+      <c r="I37" t="s">
+        <v>193</v>
+      </c>
+      <c r="J37" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>196</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>197</v>
+      </c>
+      <c r="I38" t="s">
+        <v>198</v>
+      </c>
+      <c r="J38" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s">
+        <v>202</v>
+      </c>
+      <c r="I39" t="s">
+        <v>203</v>
+      </c>
+      <c r="J39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s">
+        <v>207</v>
+      </c>
+      <c r="I40" t="s">
+        <v>208</v>
+      </c>
+      <c r="J40" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>212</v>
+      </c>
+      <c r="I41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J41" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" t="s">
+        <v>217</v>
+      </c>
+      <c r="I42" t="s">
+        <v>218</v>
+      </c>
+      <c r="J42" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>220</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>221</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" t="s">
+        <v>222</v>
+      </c>
+      <c r="I43" t="s">
+        <v>223</v>
+      </c>
+      <c r="J43" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>226</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" t="s">
+        <v>227</v>
+      </c>
+      <c r="I44" t="s">
+        <v>228</v>
+      </c>
+      <c r="J44" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>230</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>231</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" t="s">
+        <v>232</v>
+      </c>
+      <c r="I45" t="s">
+        <v>233</v>
+      </c>
+      <c r="J45" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>235</v>
+      </c>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>236</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" t="s">
+        <v>237</v>
+      </c>
+      <c r="I46" t="s">
+        <v>238</v>
+      </c>
+      <c r="J46" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>240</v>
+      </c>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>241</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
+        <v>242</v>
+      </c>
+      <c r="I47" t="s">
+        <v>243</v>
+      </c>
+      <c r="J47" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>245</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>246</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
+        <v>247</v>
+      </c>
+      <c r="I48" t="s">
+        <v>248</v>
+      </c>
+      <c r="J48" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>250</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>251</v>
+      </c>
+      <c r="F49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>252</v>
+      </c>
+      <c r="I49" t="s">
+        <v>253</v>
+      </c>
+      <c r="J49" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>255</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>257</v>
+      </c>
+      <c r="I50" t="s">
+        <v>258</v>
+      </c>
+      <c r="J50" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>260</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>261</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>262</v>
+      </c>
+      <c r="I51" t="s">
+        <v>263</v>
+      </c>
+      <c r="J51" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>265</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>266</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
+        <v>267</v>
+      </c>
+      <c r="I52" t="s">
+        <v>268</v>
+      </c>
+      <c r="J52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>270</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>271</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
+        <v>272</v>
+      </c>
+      <c r="I53" t="s">
+        <v>273</v>
+      </c>
+      <c r="J53" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>275</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>276</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
+        <v>277</v>
+      </c>
+      <c r="I54" t="s">
+        <v>278</v>
+      </c>
+      <c r="J54" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>280</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>281</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>282</v>
+      </c>
+      <c r="I55" t="s">
+        <v>283</v>
+      </c>
+      <c r="J55" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>285</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>286</v>
+      </c>
+      <c r="F56" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>287</v>
+      </c>
+      <c r="I56" t="s">
+        <v>288</v>
+      </c>
+      <c r="J56" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>290</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>291</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>292</v>
+      </c>
+      <c r="I57" t="s">
+        <v>293</v>
+      </c>
+      <c r="J57" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>296</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" t="s">
+        <v>297</v>
+      </c>
+      <c r="I58" t="s">
+        <v>298</v>
+      </c>
+      <c r="J58" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>300</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>301</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>302</v>
+      </c>
+      <c r="I59" t="s">
+        <v>303</v>
+      </c>
+      <c r="J59" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>305</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>306</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>307</v>
+      </c>
+      <c r="I60" t="s">
+        <v>308</v>
+      </c>
+      <c r="J60" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>310</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>311</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>312</v>
+      </c>
+      <c r="I61" t="s">
+        <v>313</v>
+      </c>
+      <c r="J61" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>315</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>316</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>317</v>
+      </c>
+      <c r="I62" t="s">
+        <v>318</v>
+      </c>
+      <c r="J62" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>320</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>321</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>322</v>
+      </c>
+      <c r="I63" t="s">
+        <v>323</v>
+      </c>
+      <c r="J63" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>325</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>326</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>327</v>
+      </c>
+      <c r="I64" t="s">
+        <v>328</v>
+      </c>
+      <c r="J64" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>330</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>331</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>332</v>
+      </c>
+      <c r="I65" t="s">
+        <v>333</v>
+      </c>
+      <c r="J65" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>335</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>336</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>337</v>
+      </c>
+      <c r="I66" t="s">
+        <v>338</v>
+      </c>
+      <c r="J66" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>340</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>341</v>
+      </c>
+      <c r="F67" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>342</v>
+      </c>
+      <c r="I67" t="s">
+        <v>343</v>
+      </c>
+      <c r="J67" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>345</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>346</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>347</v>
+      </c>
+      <c r="I68" t="s">
+        <v>348</v>
+      </c>
+      <c r="J68" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>350</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" t="s">
+        <v>351</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>352</v>
+      </c>
+      <c r="I69" t="s">
+        <v>353</v>
+      </c>
+      <c r="J69" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>355</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" t="s">
+        <v>356</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
+        <v>357</v>
+      </c>
+      <c r="I70" t="s">
+        <v>358</v>
+      </c>
+      <c r="J70" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>360</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" t="s">
+        <v>361</v>
+      </c>
+      <c r="F71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>362</v>
+      </c>
+      <c r="I71" t="s">
+        <v>363</v>
+      </c>
+      <c r="J71" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>365</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" t="s">
+        <v>366</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>367</v>
+      </c>
+      <c r="I72" t="s">
+        <v>368</v>
+      </c>
+      <c r="J72" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>370</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" t="s">
+        <v>371</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>372</v>
+      </c>
+      <c r="I73" t="s">
+        <v>373</v>
+      </c>
+      <c r="J73" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>375</v>
+      </c>
+      <c r="B74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" t="s">
+        <v>376</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>377</v>
+      </c>
+      <c r="I74" t="s">
+        <v>378</v>
+      </c>
+      <c r="J74" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>380</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" t="s">
+        <v>381</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>382</v>
+      </c>
+      <c r="I75" t="s">
+        <v>383</v>
+      </c>
+      <c r="J75" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>385</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>386</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>387</v>
+      </c>
+      <c r="I76" t="s">
+        <v>388</v>
+      </c>
+      <c r="J76" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>390</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" t="s">
+        <v>391</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>392</v>
+      </c>
+      <c r="I77" t="s">
+        <v>393</v>
+      </c>
+      <c r="J77" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>395</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" t="s">
+        <v>396</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>397</v>
+      </c>
+      <c r="I78" t="s">
+        <v>398</v>
+      </c>
+      <c r="J78" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>400</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" t="s">
+        <v>401</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>402</v>
+      </c>
+      <c r="I79" t="s">
+        <v>403</v>
+      </c>
+      <c r="J79" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>405</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" t="s">
+        <v>406</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" t="s">
+        <v>407</v>
+      </c>
+      <c r="I80" t="s">
+        <v>408</v>
+      </c>
+      <c r="J80" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>410</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" t="s">
+        <v>411</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>412</v>
+      </c>
+      <c r="I81" t="s">
+        <v>413</v>
+      </c>
+      <c r="J81" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>415</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>416</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>417</v>
+      </c>
+      <c r="I82" t="s">
+        <v>418</v>
+      </c>
+      <c r="J82" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>420</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" t="s">
+        <v>421</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>422</v>
+      </c>
+      <c r="I83" t="s">
+        <v>423</v>
+      </c>
+      <c r="J83" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>425</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" t="s">
+        <v>426</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>427</v>
+      </c>
+      <c r="I84" t="s">
+        <v>428</v>
+      </c>
+      <c r="J84" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>430</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" t="s">
+        <v>431</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" t="s">
+        <v>432</v>
+      </c>
+      <c r="I85" t="s">
+        <v>433</v>
+      </c>
+      <c r="J85" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>435</v>
+      </c>
+      <c r="B86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>436</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>437</v>
+      </c>
+      <c r="I86" t="s">
+        <v>438</v>
+      </c>
+      <c r="J86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>440</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>441</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>442</v>
+      </c>
+      <c r="I87" t="s">
+        <v>443</v>
+      </c>
+      <c r="J87" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>445</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" t="s">
+        <v>446</v>
+      </c>
+      <c r="F88" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
+        <v>447</v>
+      </c>
+      <c r="I88" t="s">
+        <v>448</v>
+      </c>
+      <c r="J88" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>450</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" t="s">
+        <v>451</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" t="s">
+        <v>452</v>
+      </c>
+      <c r="I89" t="s">
+        <v>453</v>
+      </c>
+      <c r="J89" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>455</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" t="s">
+        <v>456</v>
+      </c>
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" t="s">
+        <v>457</v>
+      </c>
+      <c r="I90" t="s">
+        <v>458</v>
+      </c>
+      <c r="J90" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>460</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" t="s">
+        <v>461</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" t="s">
+        <v>462</v>
+      </c>
+      <c r="I91" t="s">
+        <v>463</v>
+      </c>
+      <c r="J91" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>465</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" t="s">
+        <v>466</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
+        <v>467</v>
+      </c>
+      <c r="I92" t="s">
+        <v>468</v>
+      </c>
+      <c r="J92" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>470</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" t="s">
+        <v>471</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" t="s">
+        <v>472</v>
+      </c>
+      <c r="I93" t="s">
+        <v>473</v>
+      </c>
+      <c r="J93" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>475</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" t="s">
+        <v>476</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" t="s">
+        <v>477</v>
+      </c>
+      <c r="I94" t="s">
+        <v>478</v>
+      </c>
+      <c r="J94" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>480</v>
+      </c>
+      <c r="B95" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" t="s">
+        <v>481</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" t="s">
+        <v>482</v>
+      </c>
+      <c r="I95" t="s">
+        <v>483</v>
+      </c>
+      <c r="J95" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>485</v>
+      </c>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" t="s">
+        <v>486</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" t="s">
+        <v>487</v>
+      </c>
+      <c r="I96" t="s">
+        <v>488</v>
+      </c>
+      <c r="J96" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>490</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" t="s">
+        <v>491</v>
+      </c>
+      <c r="F97" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" t="s">
+        <v>492</v>
+      </c>
+      <c r="I97" t="s">
+        <v>493</v>
+      </c>
+      <c r="J97" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>495</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" t="s">
+        <v>496</v>
+      </c>
+      <c r="F98" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" t="s">
+        <v>497</v>
+      </c>
+      <c r="I98" t="s">
+        <v>498</v>
+      </c>
+      <c r="J98" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>500</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" t="s">
+        <v>501</v>
+      </c>
+      <c r="F99" t="s">
+        <v>14</v>
+      </c>
+      <c r="G99" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" t="s">
+        <v>502</v>
+      </c>
+      <c r="I99" t="s">
+        <v>503</v>
+      </c>
+      <c r="J99" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>505</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>506</v>
+      </c>
+      <c r="D100" t="s">
+        <v>507</v>
+      </c>
+      <c r="E100" t="s">
+        <v>508</v>
+      </c>
+      <c r="F100" t="s">
+        <v>509</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" t="s">
+        <v>510</v>
+      </c>
+      <c r="I100" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>512</v>
+      </c>
+      <c r="B101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" t="s">
+        <v>506</v>
+      </c>
+      <c r="D101" t="s">
+        <v>507</v>
+      </c>
+      <c r="E101" t="s">
+        <v>513</v>
+      </c>
+      <c r="F101" t="s">
+        <v>509</v>
+      </c>
+      <c r="G101" t="s">
+        <v>12</v>
+      </c>
+      <c r="H101" t="s">
+        <v>514</v>
+      </c>
+      <c r="I101" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>516</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" t="s">
+        <v>517</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" t="s">
+        <v>518</v>
+      </c>
+      <c r="I102" t="s">
+        <v>519</v>
+      </c>
+      <c r="J102" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>521</v>
+      </c>
+      <c r="B103" t="s">
+        <v>522</v>
+      </c>
+      <c r="C103" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" t="s">
+        <v>523</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" t="s">
+        <v>524</v>
+      </c>
+      <c r="I103" t="s">
+        <v>525</v>
+      </c>
+      <c r="J103" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>527</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" t="s">
+        <v>528</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" t="s">
+        <v>529</v>
+      </c>
+      <c r="I104" t="s">
+        <v>530</v>
+      </c>
+      <c r="J104" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>532</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" t="s">
+        <v>533</v>
+      </c>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" t="s">
+        <v>534</v>
+      </c>
+      <c r="I105" t="s">
+        <v>535</v>
+      </c>
+      <c r="J105" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>537</v>
+      </c>
+      <c r="B106" t="s">
+        <v>522</v>
+      </c>
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" t="s">
+        <v>538</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" t="s">
+        <v>539</v>
+      </c>
+      <c r="I106" t="s">
+        <v>540</v>
+      </c>
+      <c r="J106" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>542</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" t="s">
+        <v>543</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" t="s">
+        <v>544</v>
+      </c>
+      <c r="I107" t="s">
+        <v>545</v>
+      </c>
+      <c r="J107" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>547</v>
+      </c>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" t="s">
+        <v>548</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" t="s">
+        <v>549</v>
+      </c>
+      <c r="I108" t="s">
+        <v>550</v>
+      </c>
+      <c r="J108" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>552</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" t="s">
+        <v>553</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" t="s">
+        <v>554</v>
+      </c>
+      <c r="I109" t="s">
+        <v>555</v>
+      </c>
+      <c r="J109" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>557</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" t="s">
+        <v>558</v>
+      </c>
+      <c r="F110" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" t="s">
+        <v>559</v>
+      </c>
+      <c r="I110" t="s">
+        <v>560</v>
+      </c>
+      <c r="J110" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>562</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" t="s">
+        <v>563</v>
+      </c>
+      <c r="F111" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" t="s">
+        <v>564</v>
+      </c>
+      <c r="I111" t="s">
+        <v>565</v>
+      </c>
+      <c r="J111" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>567</v>
+      </c>
+      <c r="B112" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" t="s">
+        <v>568</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" t="s">
+        <v>569</v>
+      </c>
+      <c r="I112" t="s">
+        <v>570</v>
+      </c>
+      <c r="J112" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>572</v>
+      </c>
+      <c r="B113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" t="s">
+        <v>573</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" t="s">
+        <v>574</v>
+      </c>
+      <c r="I113" t="s">
+        <v>575</v>
+      </c>
+      <c r="J113" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>577</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" t="s">
+        <v>578</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" t="s">
+        <v>579</v>
+      </c>
+      <c r="I114" t="s">
+        <v>580</v>
+      </c>
+      <c r="J114" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>582</v>
+      </c>
+      <c r="B115" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" t="s">
+        <v>583</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" t="s">
+        <v>584</v>
+      </c>
+      <c r="I115" t="s">
+        <v>585</v>
+      </c>
+      <c r="J115" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>587</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" t="s">
+        <v>588</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" t="s">
+        <v>589</v>
+      </c>
+      <c r="I116" t="s">
+        <v>590</v>
+      </c>
+      <c r="J116" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>592</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" t="s">
+        <v>593</v>
+      </c>
+      <c r="F117" t="s">
+        <v>14</v>
+      </c>
+      <c r="G117" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" t="s">
+        <v>594</v>
+      </c>
+      <c r="I117" t="s">
+        <v>595</v>
+      </c>
+      <c r="J117" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>597</v>
+      </c>
+      <c r="B118" t="s">
+        <v>522</v>
+      </c>
+      <c r="C118" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" t="s">
+        <v>598</v>
+      </c>
+      <c r="F118" t="s">
+        <v>14</v>
+      </c>
+      <c r="G118" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" t="s">
+        <v>599</v>
+      </c>
+      <c r="I118" t="s">
+        <v>600</v>
+      </c>
+      <c r="J118" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>602</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" t="s">
+        <v>603</v>
+      </c>
+      <c r="F119" t="s">
+        <v>14</v>
+      </c>
+      <c r="G119" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" t="s">
+        <v>604</v>
+      </c>
+      <c r="I119" t="s">
+        <v>605</v>
+      </c>
+      <c r="J119" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>607</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s">
+        <v>608</v>
+      </c>
+      <c r="F120" t="s">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" t="s">
+        <v>609</v>
+      </c>
+      <c r="I120" t="s">
+        <v>610</v>
+      </c>
+      <c r="J120" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>612</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>613</v>
+      </c>
+      <c r="F121" t="s">
+        <v>14</v>
+      </c>
+      <c r="G121" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" t="s">
+        <v>614</v>
+      </c>
+      <c r="I121" t="s">
+        <v>615</v>
+      </c>
+      <c r="J121" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>617</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" t="s">
+        <v>618</v>
+      </c>
+      <c r="F122" t="s">
+        <v>14</v>
+      </c>
+      <c r="G122" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" t="s">
+        <v>619</v>
+      </c>
+      <c r="I122" t="s">
+        <v>620</v>
+      </c>
+      <c r="J122" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>622</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" t="s">
+        <v>623</v>
+      </c>
+      <c r="F123" t="s">
+        <v>14</v>
+      </c>
+      <c r="G123" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" t="s">
+        <v>624</v>
+      </c>
+      <c r="I123" t="s">
+        <v>625</v>
+      </c>
+      <c r="J123" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>627</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" t="s">
+        <v>628</v>
+      </c>
+      <c r="F124" t="s">
+        <v>14</v>
+      </c>
+      <c r="G124" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" t="s">
+        <v>629</v>
+      </c>
+      <c r="I124" t="s">
+        <v>630</v>
+      </c>
+      <c r="J124" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>632</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" t="s">
+        <v>633</v>
+      </c>
+      <c r="F125" t="s">
+        <v>14</v>
+      </c>
+      <c r="G125" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" t="s">
+        <v>634</v>
+      </c>
+      <c r="I125" t="s">
+        <v>635</v>
+      </c>
+      <c r="J125" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>637</v>
+      </c>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" t="s">
+        <v>638</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+      <c r="G126" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" t="s">
+        <v>639</v>
+      </c>
+      <c r="I126" t="s">
+        <v>640</v>
+      </c>
+      <c r="J126" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>642</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" t="s">
+        <v>643</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" t="s">
+        <v>644</v>
+      </c>
+      <c r="I127" t="s">
+        <v>645</v>
+      </c>
+      <c r="J127" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>647</v>
+      </c>
+      <c r="B128" t="s">
+        <v>25</v>
+      </c>
+      <c r="C128" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" t="s">
+        <v>648</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" t="s">
+        <v>649</v>
+      </c>
+      <c r="I128" t="s">
+        <v>650</v>
+      </c>
+      <c r="J128" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>652</v>
+      </c>
+      <c r="B129" t="s">
+        <v>25</v>
+      </c>
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" t="s">
+        <v>653</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>654</v>
+      </c>
+      <c r="I129" t="s">
+        <v>655</v>
+      </c>
+      <c r="J129" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>657</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" t="s">
+        <v>658</v>
+      </c>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" t="s">
+        <v>659</v>
+      </c>
+      <c r="I130" t="s">
+        <v>660</v>
+      </c>
+      <c r="J130" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>662</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" t="s">
+        <v>663</v>
+      </c>
+      <c r="F131" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" t="s">
+        <v>664</v>
+      </c>
+      <c r="I131" t="s">
+        <v>665</v>
+      </c>
+      <c r="J131" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>667</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" t="s">
+        <v>668</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" t="s">
+        <v>669</v>
+      </c>
+      <c r="I132" t="s">
+        <v>670</v>
+      </c>
+      <c r="J132" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>672</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" t="s">
+        <v>673</v>
+      </c>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" t="s">
+        <v>674</v>
+      </c>
+      <c r="I133" t="s">
+        <v>675</v>
+      </c>
+      <c r="J133" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>677</v>
+      </c>
+      <c r="B134" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" t="s">
+        <v>678</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" t="s">
+        <v>679</v>
+      </c>
+      <c r="I134" t="s">
+        <v>680</v>
+      </c>
+      <c r="J134" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>682</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" t="s">
+        <v>683</v>
+      </c>
+      <c r="F135" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" t="s">
+        <v>684</v>
+      </c>
+      <c r="I135" t="s">
+        <v>685</v>
+      </c>
+      <c r="J135" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>687</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" t="s">
+        <v>688</v>
+      </c>
+      <c r="F136" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" t="s">
+        <v>689</v>
+      </c>
+      <c r="I136" t="s">
+        <v>690</v>
+      </c>
+      <c r="J136" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>692</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" t="s">
+        <v>12</v>
+      </c>
+      <c r="E137" t="s">
+        <v>693</v>
+      </c>
+      <c r="F137" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" t="s">
+        <v>694</v>
+      </c>
+      <c r="I137" t="s">
+        <v>695</v>
+      </c>
+      <c r="J137" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>697</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" t="s">
+        <v>698</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" t="s">
+        <v>699</v>
+      </c>
+      <c r="I138" t="s">
+        <v>700</v>
+      </c>
+      <c r="J138" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>702</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" t="s">
+        <v>12</v>
+      </c>
+      <c r="E139" t="s">
+        <v>703</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" t="s">
+        <v>704</v>
+      </c>
+      <c r="I139" t="s">
+        <v>705</v>
+      </c>
+      <c r="J139" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>707</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" t="s">
+        <v>12</v>
+      </c>
+      <c r="E140" t="s">
+        <v>708</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" t="s">
+        <v>709</v>
+      </c>
+      <c r="I140" t="s">
+        <v>710</v>
+      </c>
+      <c r="J140" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>712</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" t="s">
+        <v>713</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" t="s">
+        <v>714</v>
+      </c>
+      <c r="I141" t="s">
+        <v>715</v>
+      </c>
+      <c r="J141" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>717</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" t="s">
+        <v>718</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" t="s">
+        <v>719</v>
+      </c>
+      <c r="I142" t="s">
+        <v>720</v>
+      </c>
+      <c r="J142" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>722</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" t="s">
+        <v>723</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" t="s">
+        <v>724</v>
+      </c>
+      <c r="I143" t="s">
+        <v>725</v>
+      </c>
+      <c r="J143" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>727</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" t="s">
+        <v>728</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" t="s">
+        <v>729</v>
+      </c>
+      <c r="I144" t="s">
+        <v>730</v>
+      </c>
+      <c r="J144" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>732</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" t="s">
+        <v>733</v>
+      </c>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" t="s">
+        <v>734</v>
+      </c>
+      <c r="I145" t="s">
+        <v>735</v>
+      </c>
+      <c r="J145" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>737</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" t="s">
+        <v>12</v>
+      </c>
+      <c r="E146" t="s">
+        <v>738</v>
+      </c>
+      <c r="F146" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" t="s">
+        <v>739</v>
+      </c>
+      <c r="I146" t="s">
+        <v>740</v>
+      </c>
+      <c r="J146" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>742</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" t="s">
+        <v>743</v>
+      </c>
+      <c r="F147" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" t="s">
+        <v>744</v>
+      </c>
+      <c r="I147" t="s">
+        <v>745</v>
+      </c>
+      <c r="J147" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>746</v>
+      </c>
+      <c r="B148" t="s">
+        <v>522</v>
+      </c>
+      <c r="C148" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" t="s">
+        <v>747</v>
+      </c>
+      <c r="F148" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" t="s">
+        <v>748</v>
+      </c>
+      <c r="I148" t="s">
+        <v>749</v>
+      </c>
+      <c r="J148" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>751</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" t="s">
+        <v>752</v>
+      </c>
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" t="s">
+        <v>753</v>
+      </c>
+      <c r="I149" t="s">
+        <v>754</v>
+      </c>
+      <c r="J149" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>756</v>
+      </c>
+      <c r="B150" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" t="s">
+        <v>12</v>
+      </c>
+      <c r="E150" t="s">
+        <v>757</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" t="s">
+        <v>758</v>
+      </c>
+      <c r="I150" t="s">
+        <v>759</v>
+      </c>
+      <c r="J150" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>760</v>
+      </c>
+      <c r="B151" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" t="s">
+        <v>761</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" t="s">
+        <v>762</v>
+      </c>
+      <c r="I151" t="s">
+        <v>763</v>
+      </c>
+      <c r="J151" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>765</v>
+      </c>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" t="s">
+        <v>766</v>
+      </c>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" t="s">
+        <v>767</v>
+      </c>
+      <c r="I152" t="s">
+        <v>768</v>
+      </c>
+      <c r="J152" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>770</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" t="s">
+        <v>12</v>
+      </c>
+      <c r="E153" t="s">
+        <v>771</v>
+      </c>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" t="s">
+        <v>772</v>
+      </c>
+      <c r="I153" t="s">
+        <v>773</v>
+      </c>
+      <c r="J153" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>775</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" t="s">
+        <v>776</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" t="s">
+        <v>777</v>
+      </c>
+      <c r="I154" t="s">
+        <v>778</v>
+      </c>
+      <c r="J154" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>780</v>
+      </c>
+      <c r="B155" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" t="s">
+        <v>781</v>
+      </c>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" t="s">
+        <v>782</v>
+      </c>
+      <c r="I155" t="s">
+        <v>783</v>
+      </c>
+      <c r="J155" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>785</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" t="s">
+        <v>12</v>
+      </c>
+      <c r="E156" t="s">
+        <v>786</v>
+      </c>
+      <c r="F156" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" t="s">
+        <v>787</v>
+      </c>
+      <c r="I156" t="s">
+        <v>788</v>
+      </c>
+      <c r="J156" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>790</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" t="s">
+        <v>12</v>
+      </c>
+      <c r="E157" t="s">
+        <v>791</v>
+      </c>
+      <c r="F157" t="s">
+        <v>14</v>
+      </c>
+      <c r="G157" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" t="s">
+        <v>792</v>
+      </c>
+      <c r="I157" t="s">
+        <v>793</v>
+      </c>
+      <c r="J157" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>795</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" t="s">
+        <v>12</v>
+      </c>
+      <c r="E158" t="s">
+        <v>796</v>
+      </c>
+      <c r="F158" t="s">
+        <v>14</v>
+      </c>
+      <c r="G158" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
+        <v>797</v>
+      </c>
+      <c r="I158" t="s">
+        <v>798</v>
+      </c>
+      <c r="J158" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>800</v>
+      </c>
+      <c r="B159" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159" t="s">
+        <v>12</v>
+      </c>
+      <c r="E159" t="s">
+        <v>801</v>
+      </c>
+      <c r="F159" t="s">
+        <v>14</v>
+      </c>
+      <c r="G159" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" t="s">
+        <v>802</v>
+      </c>
+      <c r="I159" t="s">
+        <v>803</v>
+      </c>
+      <c r="J159" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>805</v>
+      </c>
+      <c r="B160" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" t="s">
+        <v>806</v>
+      </c>
+      <c r="F160" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" t="s">
+        <v>807</v>
+      </c>
+      <c r="I160" t="s">
+        <v>808</v>
+      </c>
+      <c r="J160" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>810</v>
+      </c>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" t="s">
+        <v>12</v>
+      </c>
+      <c r="E161" t="s">
+        <v>811</v>
+      </c>
+      <c r="F161" t="s">
+        <v>14</v>
+      </c>
+      <c r="G161" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" t="s">
+        <v>812</v>
+      </c>
+      <c r="I161" t="s">
+        <v>478</v>
+      </c>
+      <c r="J161" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>814</v>
+      </c>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" t="s">
+        <v>12</v>
+      </c>
+      <c r="E162" t="s">
+        <v>815</v>
+      </c>
+      <c r="F162" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" t="s">
+        <v>816</v>
+      </c>
+      <c r="I162" t="s">
+        <v>817</v>
+      </c>
+      <c r="J162" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>819</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" t="s">
+        <v>820</v>
+      </c>
+      <c r="F163" t="s">
+        <v>14</v>
+      </c>
+      <c r="G163" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" t="s">
+        <v>821</v>
+      </c>
+      <c r="I163" t="s">
+        <v>822</v>
+      </c>
+      <c r="J163" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>824</v>
+      </c>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" t="s">
+        <v>825</v>
+      </c>
+      <c r="F164" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" t="s">
+        <v>826</v>
+      </c>
+      <c r="I164" t="s">
+        <v>827</v>
+      </c>
+      <c r="J164" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>829</v>
+      </c>
+      <c r="B165" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" t="s">
+        <v>830</v>
+      </c>
+      <c r="F165" t="s">
+        <v>14</v>
+      </c>
+      <c r="G165" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" t="s">
+        <v>831</v>
+      </c>
+      <c r="I165" t="s">
+        <v>832</v>
+      </c>
+      <c r="J165" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>834</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" t="s">
+        <v>835</v>
+      </c>
+      <c r="F166" t="s">
+        <v>14</v>
+      </c>
+      <c r="G166" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" t="s">
+        <v>836</v>
+      </c>
+      <c r="I166" t="s">
+        <v>837</v>
+      </c>
+      <c r="J166" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>839</v>
+      </c>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167" t="s">
+        <v>12</v>
+      </c>
+      <c r="E167" t="s">
+        <v>840</v>
+      </c>
+      <c r="F167" t="s">
+        <v>14</v>
+      </c>
+      <c r="G167" t="s">
+        <v>15</v>
+      </c>
+      <c r="H167" t="s">
+        <v>841</v>
+      </c>
+      <c r="I167" t="s">
+        <v>842</v>
+      </c>
+      <c r="J167" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>844</v>
+      </c>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168" t="s">
+        <v>12</v>
+      </c>
+      <c r="E168" t="s">
+        <v>845</v>
+      </c>
+      <c r="F168" t="s">
+        <v>14</v>
+      </c>
+      <c r="G168" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" t="s">
+        <v>846</v>
+      </c>
+      <c r="I168" t="s">
+        <v>847</v>
+      </c>
+      <c r="J168" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>849</v>
+      </c>
+      <c r="B169" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" t="s">
+        <v>12</v>
+      </c>
+      <c r="E169" t="s">
+        <v>850</v>
+      </c>
+      <c r="F169" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" t="s">
+        <v>851</v>
+      </c>
+      <c r="I169" t="s">
+        <v>852</v>
+      </c>
+      <c r="J169" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>854</v>
+      </c>
+      <c r="B170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" t="s">
+        <v>12</v>
+      </c>
+      <c r="E170" t="s">
+        <v>855</v>
+      </c>
+      <c r="F170" t="s">
+        <v>14</v>
+      </c>
+      <c r="G170" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" t="s">
+        <v>856</v>
+      </c>
+      <c r="I170" t="s">
+        <v>857</v>
+      </c>
+      <c r="J170" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>859</v>
+      </c>
+      <c r="B171" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171" t="s">
+        <v>12</v>
+      </c>
+      <c r="E171" t="s">
+        <v>860</v>
+      </c>
+      <c r="F171" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" t="s">
+        <v>861</v>
+      </c>
+      <c r="I171" t="s">
+        <v>862</v>
+      </c>
+      <c r="J171" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>864</v>
+      </c>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" t="s">
+        <v>12</v>
+      </c>
+      <c r="E172" t="s">
+        <v>865</v>
+      </c>
+      <c r="F172" t="s">
+        <v>14</v>
+      </c>
+      <c r="G172" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" t="s">
+        <v>866</v>
+      </c>
+      <c r="I172" t="s">
+        <v>493</v>
+      </c>
+      <c r="J172" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>868</v>
+      </c>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173" t="s">
+        <v>869</v>
+      </c>
+      <c r="F173" t="s">
+        <v>14</v>
+      </c>
+      <c r="G173" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" t="s">
+        <v>870</v>
+      </c>
+      <c r="I173" t="s">
+        <v>871</v>
+      </c>
+      <c r="J173" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>873</v>
+      </c>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174" t="s">
+        <v>874</v>
+      </c>
+      <c r="F174" t="s">
+        <v>14</v>
+      </c>
+      <c r="G174" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" t="s">
+        <v>875</v>
+      </c>
+      <c r="I174" t="s">
+        <v>876</v>
+      </c>
+      <c r="J174" t="s">
+        <v>877</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/tools/importer/reports/import-press-release.report.xlsx
+++ b/tools/importer/reports/import-press-release.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1008">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,7 +61,7 @@
     <t>press-release</t>
   </si>
   <si>
-    <t>2026-04-05T02:55:15.720Z</t>
+    <t>2026-04-24T10:06:24.578Z</t>
   </si>
   <si>
     <t>Acalabrutinib raccomandato in Europa per la designazione di Farmaco Orfano in tre indicazioni</t>
@@ -76,7 +76,7 @@
     <t>area-stampa/press-releases/2016/accordo-cilag</t>
   </si>
   <si>
-    <t>2026-04-05T00:23:29.854Z</t>
+    <t>2026-04-24T09:39:53.269Z</t>
   </si>
   <si>
     <t>AstraZeneca completa l’accordo con Cilag Gmbh International per i diritti su budesonide al di fuori degli Stati Uniti</t>
@@ -109,7 +109,7 @@
     <t>area-stampa/press-releases/2016/accordoolaparivconfmi</t>
   </si>
   <si>
-    <t>2026-04-05T00:24:04.873Z</t>
+    <t>2026-04-24T09:51:02.825Z</t>
   </si>
   <si>
     <t>AstraZeneca e Foundation Medicine danno il via a una collaborazione strategica per il test diagnostico abbinato per olaparib</t>
@@ -124,7 +124,7 @@
     <t>area-stampa/press-releases/2016/acerta-pharma</t>
   </si>
   <si>
-    <t>2026-04-05T00:24:39.741Z</t>
+    <t>2026-04-24T10:08:12.235Z</t>
   </si>
   <si>
     <t>AstraZeneca completa la transazione per l’acquisizione della partecipazione azionaria di maggioranza in Acerta Pharma</t>
@@ -154,7 +154,7 @@
     <t>area-stampa/press-releases/2016/aralez</t>
   </si>
   <si>
-    <t>2026-04-05T02:55:50.738Z</t>
+    <t>2026-04-24T09:43:25.776Z</t>
   </si>
   <si>
     <t>Negli Stati Uniti, AstraZeneca stringe un accordo con Aralez per metoprololo succinato</t>
@@ -169,7 +169,7 @@
     <t>area-stampa/press-releases/2016/astrazeneca-stipula-due-accordi-di-licenza-con-leo-pharmap-er-il-trattamento-delle-malattie-cutanee</t>
   </si>
   <si>
-    <t>2026-04-05T02:56:27.030Z</t>
+    <t>2026-04-24T09:49:51.184Z</t>
   </si>
   <si>
     <t>AstraZeneca stipula due accordi di licenza con Leo Pharma per il trattamento delle malattie cutanee</t>
@@ -199,7 +199,7 @@
     <t>area-stampa/press-releases/2016/benralizumabers</t>
   </si>
   <si>
-    <t>2026-04-05T00:25:48.877Z</t>
+    <t>2026-04-24T09:46:53.737Z</t>
   </si>
   <si>
     <t>Asma grave. Benralizumab dimostra risultati positivi in alcuni trial di fase III presentati al congresso ERS 2016</t>
@@ -229,7 +229,7 @@
     <t>area-stampa/press-releases/2016/cediranib</t>
   </si>
   <si>
-    <t>2026-04-05T00:26:24.642Z</t>
+    <t>2026-04-24T09:45:09.808Z</t>
   </si>
   <si>
     <t>Da AstraZeneca un aggiornamento sulla domanda di autorizzazione all’immissione in commercio di cediranib nell’Unione Europea</t>
@@ -244,7 +244,7 @@
     <t>area-stampa/press-releases/2016/ceftazidime-avibactam-approvato-nell-unione-europea-per-il-trattamento-dei-pazienti-con-gravi-infezioni-batteriche</t>
   </si>
   <si>
-    <t>2026-04-05T00:26:59.106Z</t>
+    <t>2026-04-24T09:50:26.474Z</t>
   </si>
   <si>
     <t>Ceftazidime/avibactam approvato nell’Unione Europea per il trattamento dei pazienti con gravi infezioni batteriche</t>
@@ -259,7 +259,7 @@
     <t>area-stampa/press-releases/2016/ceftazidime-avibactam</t>
   </si>
   <si>
-    <t>2026-04-05T00:27:33.830Z</t>
+    <t>2026-04-24T09:48:41.353Z</t>
   </si>
   <si>
     <t>L’antibiotico ceftazidime-avibactam raggiunge gli endpoint primari nello studio di fase III per il trattamento della polmonite acquisita in ospedale</t>
@@ -274,7 +274,7 @@
     <t>area-stampa/press-releases/2016/congressiscientifici</t>
   </si>
   <si>
-    <t>2026-04-05T02:57:39.012Z</t>
+    <t>2026-04-24T09:40:28.369Z</t>
   </si>
   <si>
     <t>Oncologia: AstraZeneca protagonista nei principali congressi scientifici negli Stati Uniti ed in Europa</t>
@@ -289,7 +289,7 @@
     <t>area-stampa/press-releases/2016/consorzio-rcp2</t>
   </si>
   <si>
-    <t>2026-04-05T02:58:13.380Z</t>
+    <t>2026-04-24T10:07:36.403Z</t>
   </si>
   <si>
     <t>AstraZeneca e MedImmune istituiscono un consorzio per offrire nuovi trattamenti per la nefropatia cronica</t>
@@ -304,7 +304,7 @@
     <t>area-stampa/press-releases/2016/dapagliflozin</t>
   </si>
   <si>
-    <t>2026-04-05T00:28:08.736Z</t>
+    <t>2026-04-24T09:46:19.686Z</t>
   </si>
   <si>
     <t>Dapagliflozin protagonista di due nuovi trial di fase IIIb per il trattamento dell’insufficienza renale cronica e dello scompenso cardiaco cronico</t>
@@ -319,7 +319,7 @@
     <t>area-stampa/press-releases/2016/davidgoldstein</t>
   </si>
   <si>
-    <t>2026-04-05T02:58:49.752Z</t>
+    <t>2026-04-24T09:44:34.716Z</t>
   </si>
   <si>
     <t>AstraZeneca nomina David Goldstein come chief advisor per la sua iniziativa sulla genomica</t>
@@ -334,7 +334,7 @@
     <t>area-stampa/press-releases/2016/durvalumab-breakthroughtherapy</t>
   </si>
   <si>
-    <t>2026-04-05T00:28:43.977Z</t>
+    <t>2026-04-24T10:05:14.306Z</t>
   </si>
   <si>
     <t>Durvalumab ha ottenuto la designazione di Breakthrough Therapy dalla FDA Americana per il trattamento del carcinoma uroteliale della vescica PD-L1-positivo</t>
@@ -349,7 +349,7 @@
     <t>area-stampa/press-releases/2016/durvalumab</t>
   </si>
   <si>
-    <t>2026-04-05T13:23:40.446Z</t>
+    <t>2026-04-24T09:39:17.765Z</t>
   </si>
   <si>
     <t>Accettata dalla FDA la prima domanda di licenza per durvalumab per il trattamento del tumore alla vescica</t>
@@ -364,7 +364,7 @@
     <t>area-stampa/press-releases/2016/durvalumabasco2016</t>
   </si>
   <si>
-    <t>2026-04-05T03:00:00.211Z</t>
+    <t>2026-04-24T09:52:12.808Z</t>
   </si>
   <si>
     <t>ASCO 2016 – La monoterapia con durvalumab efficace nel tumore uroteliale della vescica</t>
@@ -379,7 +379,7 @@
     <t>area-stampa/press-releases/2016/durvalumabesmo</t>
   </si>
   <si>
-    <t>2026-04-05T13:13:14.470Z</t>
+    <t>2026-04-24T09:42:16.482Z</t>
   </si>
   <si>
     <t>ESMO 2016: durvalumab mostra dati iniziali promettenti per il trattamento del tumore al polmone e del tumore testa collo</t>
@@ -394,7 +394,7 @@
     <t>area-stampa/press-releases/2016/eccmid-2016</t>
   </si>
   <si>
-    <t>2026-04-05T00:18:52.323Z</t>
+    <t>2026-04-24T09:58:36.123Z</t>
   </si>
   <si>
     <t>Un’analisi aggregata di sette studi clinici dimostra l’efficacia consistente di ceftazidime-avibactam nel trattamento di batteri Gram-negativi multi resistenti</t>
@@ -409,7 +409,7 @@
     <t>area-stampa/press-releases/2016/elcc-osimertinib</t>
   </si>
   <si>
-    <t>2026-04-05T00:29:18.644Z</t>
+    <t>2026-04-24T09:59:47.310Z</t>
   </si>
   <si>
     <t>European Lung Cancer Conference 2016: AstraZeneca presenta dati positivi di follow-up su osimertinib nel tumore al polmone</t>
@@ -424,7 +424,7 @@
     <t>area-stampa/press-releases/2016/euclid</t>
   </si>
   <si>
-    <t>2026-04-05T00:29:53.726Z</t>
+    <t>2026-04-24T09:42:51.258Z</t>
   </si>
   <si>
     <t>AstraZeneca pubblica i risultati principali dello studio EUCLID sull’utilizzo di ticagrelor nel trattamento dell’arteriopatia obliterante periferica</t>
@@ -439,7 +439,7 @@
     <t>area-stampa/press-releases/2016/exenatide</t>
   </si>
   <si>
-    <t>2026-04-05T00:30:29.875Z</t>
+    <t>2026-04-24T09:45:44.331Z</t>
   </si>
   <si>
     <t>Diabete. La combinazione di exenatide a rilascio prolungato e dapagliflozin in pazienti con Diabete di tipo 2 ha dimostrato benefici significativi in un trial di fase III.</t>
@@ -454,7 +454,7 @@
     <t>area-stampa/press-releases/2016/fda-glicopirrolato</t>
   </si>
   <si>
-    <t>2026-04-05T00:19:27.726Z</t>
+    <t>2026-04-24T09:58:00.989Z</t>
   </si>
   <si>
     <t>La FDA approva la combinazione di glicopirrolato e formoterolo fumarato per il trattamento dei pazienti con BPCO</t>
@@ -469,7 +469,7 @@
     <t>area-stampa/press-releases/2016/felodipina</t>
   </si>
   <si>
-    <t>2026-04-05T00:31:03.815Z</t>
+    <t>2026-04-24T10:04:38.701Z</t>
   </si>
   <si>
     <t>AstraZeneca stipula un contratto di licenza con China Medical System Holdings per un farmaco contro l’ipertensione</t>
@@ -484,7 +484,7 @@
     <t>area-stampa/press-releases/2016/fulvestrant-esmo</t>
   </si>
   <si>
-    <t>2026-04-05T00:32:12.677Z</t>
+    <t>2026-04-24T09:44:00.142Z</t>
   </si>
   <si>
     <t>ESMO 2016: Fulvestrant dimostra benefici significativi nella sopravvivenza libera da progressione nel trattamento di prima linea per il tumore al seno in stadio avanzato</t>
@@ -499,7 +499,7 @@
     <t>area-stampa/press-releases/2016/fulvestrant-falcon</t>
   </si>
   <si>
-    <t>2026-04-05T00:20:03.059Z</t>
+    <t>2026-04-24T09:54:30.117Z</t>
   </si>
   <si>
     <t>Fulvestrant raggiunge l’endpoint primario nel trattamento di prima linea del tumore al seno avanzato o metastatico</t>
@@ -529,7 +529,7 @@
     <t>area-stampa/press-releases/2016/incyte</t>
   </si>
   <si>
-    <t>2026-04-05T00:32:47.867Z</t>
+    <t>2026-04-24T10:09:58.800Z</t>
   </si>
   <si>
     <t>AstraZeneca e Incyte annunciano una nuova collaborazione per uno studio clinico sul tumore al polmone</t>
@@ -544,7 +544,7 @@
     <t>area-stampa/press-releases/2016/ironwwod</t>
   </si>
   <si>
-    <t>2026-04-05T00:33:23.787Z</t>
+    <t>2026-04-24T09:57:26.307Z</t>
   </si>
   <si>
     <t>AstraZeneca stipula un contratto di licenza con Ironwood Pharmaceuticals per lesinurad negli Stati Uniti</t>
@@ -559,7 +559,7 @@
     <t>area-stampa/press-releases/2016/lesinurad</t>
   </si>
   <si>
-    <t>2026-04-05T03:00:35.079Z</t>
+    <t>2026-04-24T10:05:49.363Z</t>
   </si>
   <si>
     <t>Lesinurad approvato in Europa per il trattamento dei pazienti affetti da gotta</t>
@@ -574,7 +574,7 @@
     <t>area-stampa/press-releases/2016/lesinurad1</t>
   </si>
   <si>
-    <t>2026-04-05T03:01:09.761Z</t>
+    <t>2026-04-24T09:51:38.321Z</t>
   </si>
   <si>
     <t>AstraZeneca concede la licenza di lesinurad a Grünenthal GmbH in Europa e America Latina</t>
@@ -589,7 +589,7 @@
     <t>area-stampa/press-releases/2016/linee-guida-acc-aha-ticagrelor</t>
   </si>
   <si>
-    <t>2026-04-05T00:20:38.337Z</t>
+    <t>2026-04-24T10:00:23.359Z</t>
   </si>
   <si>
     <t>Ticagrelor raccomandato rispetto a clopidogrel nelle linee guida aggiornate dell’American College of Cardiology e dell’American Heart Association sulla Sindrome Coronarica Acuta</t>
@@ -604,7 +604,7 @@
     <t>area-stampa/press-releases/2016/lynparza-breakthroughtherapy</t>
   </si>
   <si>
-    <t>2026-04-05T00:34:00.180Z</t>
+    <t>2026-04-24T10:07:00.279Z</t>
   </si>
   <si>
     <t>Olaparib ottiene la designazione di Breakthrough Therapy dalla FDA statunitense per il trattamento del tumore alla prostata metastatico resistente alla castrazione con mutazione dei geni BRCA1/2 o ATM</t>
@@ -619,7 +619,7 @@
     <t>area-stampa/press-releases/2016/medi551-orphan-drug</t>
   </si>
   <si>
-    <t>2026-04-05T00:21:12.292Z</t>
+    <t>2026-04-24T10:04:03.435Z</t>
   </si>
   <si>
     <t>Il farmaco di AstraZeneca in fase di sviluppo per la neuromielite ottica riceve la designazione di medicinale orfano dalla FDA</t>
@@ -634,7 +634,7 @@
     <t>area-stampa/press-releases/2016/medi8852-fda-fast-track</t>
   </si>
   <si>
-    <t>2026-04-05T00:21:47.283Z</t>
+    <t>2026-04-24T10:02:43.629Z</t>
   </si>
   <si>
     <t>Medimmune riceve la designazione Fast Track negli Stati Uniti per MEDI8852 per il trattamento dei pazienti ricoverati con influenza A</t>
@@ -649,7 +649,7 @@
     <t>area-stampa/press-releases/2016/moderna-therapeutics</t>
   </si>
   <si>
-    <t>2026-04-05T00:34:35.928Z</t>
+    <t>2026-04-24T10:08:48.281Z</t>
   </si>
   <si>
     <t>AstraZeneca e Moderna Therapeutics annunciano una nuova collaborazione per lo sviluppo e la commercializzazione congiunta delle terapie immuno-oncologiche mRNA Therapeutics™</t>
@@ -664,7 +664,7 @@
     <t>area-stampa/press-releases/2016/moventig-prostrakan</t>
   </si>
   <si>
-    <t>2026-04-05T03:01:44.736Z</t>
+    <t>2026-04-24T10:02:09.288Z</t>
   </si>
   <si>
     <t>AstraZeneca stipula un accordo con Prostrakan per i diritti su naloxegol in Europa</t>
@@ -679,7 +679,7 @@
     <t>area-stampa/press-releases/2016/olaparib-gold</t>
   </si>
   <si>
-    <t>2026-04-05T00:35:10.353Z</t>
+    <t>2026-04-24T09:55:39.555Z</t>
   </si>
   <si>
     <t>Pubblicati i risultati principali del trial GOLD su olaparib per il trattamento del tumore gastrico avanzato</t>
@@ -694,7 +694,7 @@
     <t>area-stampa/press-releases/2016/olaparib</t>
   </si>
   <si>
-    <t>2026-04-05T03:21:01.401Z</t>
+    <t>2026-04-24T09:59:11.804Z</t>
   </si>
   <si>
     <t>Tumore ovarico: arriva in Italia la terapia contro la “mutazione Jolie”</t>
@@ -709,7 +709,7 @@
     <t>area-stampa/press-releases/2016/olaparibasco2016</t>
   </si>
   <si>
-    <t>2026-04-05T00:35:45.639Z</t>
+    <t>2026-04-24T09:52:46.589Z</t>
   </si>
   <si>
     <t>ASCO 2016 – Olaparib: gli ultimi dati suggeriscono un potenziale vantaggio in termini di sopravvivenza globale nelle pazienti con tumore ovarico platino-sensibile</t>
@@ -724,7 +724,7 @@
     <t>area-stampa/press-releases/2016/olaparibsolo2</t>
   </si>
   <si>
-    <t>2026-04-05T00:36:21.657Z</t>
+    <t>2026-04-24T09:41:40.881Z</t>
   </si>
   <si>
     <t>Nuove e ulteriori conferme per olaparib: il trial di fase III SOLO-2 dimostra vantaggi significativi in termini di sopravvivenza libera da progressione</t>
@@ -739,7 +739,7 @@
     <t>area-stampa/press-releases/2016/osimertinib-aura3</t>
   </si>
   <si>
-    <t>2026-04-05T03:02:19.795Z</t>
+    <t>2026-04-24T09:49:15.481Z</t>
   </si>
   <si>
     <t>Tumore al polmone: osimertinib raggiunge l’endpoint primario nel trial di fase III AURA3</t>
@@ -754,7 +754,7 @@
     <t>area-stampa/press-releases/2016/osimertinib-ce</t>
   </si>
   <si>
-    <t>2026-04-05T13:13:48.744Z</t>
+    <t>2026-04-24T10:12:20.160Z</t>
   </si>
   <si>
     <t>Osimertinib approvato in Europa come primo trattamento di una nuova classe terapeutica per i pazienti con tumore al polmone non a piccole cellule metastatico positivo alla mutazione T790M dell’EGFR</t>
@@ -769,7 +769,7 @@
     <t>area-stampa/press-releases/2016/osimertinibasco2016</t>
   </si>
   <si>
-    <t>2026-04-05T00:36:56.380Z</t>
+    <t>2026-04-24T09:53:20.761Z</t>
   </si>
   <si>
     <t>ASCO 2016 – Osimertinib mostra attività clinica nei pazienti con localizzazione leptomeningea del tumore al polmone</t>
@@ -784,7 +784,7 @@
     <t>area-stampa/press-releases/2016/pfizer</t>
   </si>
   <si>
-    <t>2026-04-05T13:12:02.997Z</t>
+    <t>2026-04-24T09:48:05.902Z</t>
   </si>
   <si>
     <t>AstraZeneca vende a Pfizer il proprio business di antibiotici a piccole molecole</t>
@@ -799,7 +799,7 @@
     <t>area-stampa/press-releases/2016/plaiv-chmp</t>
   </si>
   <si>
-    <t>2026-04-05T02:54:05.583Z</t>
+    <t>2026-04-24T10:00:58.680Z</t>
   </si>
   <si>
     <t>Parere positivo del CHMP per il vaccino contro l’influenza pandemica</t>
@@ -814,7 +814,7 @@
     <t>area-stampa/press-releases/2016/ricerca-traslazionale</t>
   </si>
   <si>
-    <t>2026-04-05T00:37:31.312Z</t>
+    <t>2026-04-24T10:09:24.493Z</t>
   </si>
   <si>
     <t>AstraZeneca avvia una collaborazione con aziende del settore e il mondo accademico per creare un fondo per la ricerca traslazionale</t>
@@ -829,7 +829,7 @@
     <t>area-stampa/press-releases/2016/ricercagenomica</t>
   </si>
   <si>
-    <t>2026-04-05T00:38:06.450Z</t>
+    <t>2026-04-24T09:56:51.442Z</t>
   </si>
   <si>
     <t>AstraZeneca: al via una nuova iniziativa genomica integrata per trasformare la scoperta e lo sviluppo di farmaci</t>
@@ -844,7 +844,7 @@
     <t>area-stampa/press-releases/2016/risultati-socrates</t>
   </si>
   <si>
-    <t>2026-04-05T00:38:43.004Z</t>
+    <t>2026-04-24T10:01:33.131Z</t>
   </si>
   <si>
     <t>AstraZeneca pubblica i risultati principali del trial SOCRATES che ha studiato ticagrelor nella prevenzione secondaria dell’ictus</t>
@@ -859,7 +859,7 @@
     <t>area-stampa/press-releases/2016/saxa-dapa-chmp</t>
   </si>
   <si>
-    <t>2026-04-05T00:22:21.632Z</t>
+    <t>2026-04-24T09:53:55.491Z</t>
   </si>
   <si>
     <t>Parere positivo del CHMP per la combinazione saxagliptin e dapagliflozin per il trattamento di pazienti adulti con diabete di tipo 2</t>
@@ -874,7 +874,7 @@
     <t>area-stampa/press-releases/2016/secretomics</t>
   </si>
   <si>
-    <t>2026-04-05T00:39:19.155Z</t>
+    <t>2026-04-24T10:10:34.143Z</t>
   </si>
   <si>
     <t>AstraZeneca sfrutta le potenzialità del secretoma per lo sviluppo di farmaci biologici di nuova generazione in collaborazione con il nuovo Wallenberg Centre for Protein Research</t>
@@ -889,7 +889,7 @@
     <t>area-stampa/press-releases/2016/selumetinib-farmacoorfano</t>
   </si>
   <si>
-    <t>2026-04-05T00:40:29.378Z</t>
+    <t>2026-04-24T09:56:15.145Z</t>
   </si>
   <si>
     <t>Selumetinib riceve la designazione di farmaco orfano negli Stati Uniti per la terapia adiuvante del tumore differenziato della tiroide</t>
@@ -904,7 +904,7 @@
     <t>area-stampa/press-releases/2016/selumetinib</t>
   </si>
   <si>
-    <t>2026-04-05T00:39:53.625Z</t>
+    <t>2026-04-24T09:47:29.626Z</t>
   </si>
   <si>
     <t>AstraZeneca pubblica un aggiornamento sul trial di fase III che ha valutato l’utilizzo di selumetinib nel trattamento del tumore al polmone non a piccole cellule (NSCLC)</t>
@@ -919,7 +919,7 @@
     <t>area-stampa/press-releases/2016/takeda</t>
   </si>
   <si>
-    <t>2026-04-05T03:02:55.320Z</t>
+    <t>2026-04-24T09:55:04.062Z</t>
   </si>
   <si>
     <t>AstraZeneca completa l’acquisizione della divisione malattie respiratorie di Takeda</t>
@@ -934,7 +934,7 @@
     <t>area-stampa/press-releases/2016/testbrca</t>
   </si>
   <si>
-    <t>2026-04-05T00:41:05.420Z</t>
+    <t>2026-04-24T09:41:04.381Z</t>
   </si>
   <si>
     <t>La lotta al tumore ovarico passa dal diritto al test genetico BRCA. Al via tre progetti nazionali: Società Scientifiche e Associazioni Pazienti dimostrano la necessità di garantire un accesso omogeneo al test in tutta Italia, per le pazienti e per la prevenzione dei famigliari. Appello forte alla Regione Lombardia: si chiede di “Scegliere di Sapere”.</t>
@@ -949,7 +949,7 @@
     <t>area-stampa/press-releases/2016/top-employer</t>
   </si>
   <si>
-    <t>2026-04-05T02:54:40.743Z</t>
+    <t>2026-04-24T10:11:44.619Z</t>
   </si>
   <si>
     <t>Anche nel 2016 AstraZeneca ottiene la certificazione “Top Employers Italia”</t>
@@ -964,7 +964,7 @@
     <t>area-stampa/press-releases/2016/voluntis</t>
   </si>
   <si>
-    <t>2026-04-05T00:22:55.363Z</t>
+    <t>2026-04-24T10:11:09.150Z</t>
   </si>
   <si>
     <t>AstraZeneca e Voluntis in collaborazione con il National Cancer Institute Statunitense testano un’app di supporto negli studi sul cancro ovarico</t>
@@ -979,7 +979,7 @@
     <t>area-stampa/press-releases/2017/aacr-oncologia</t>
   </si>
   <si>
-    <t>2026-04-06T04:13:06.347Z</t>
+    <t>2026-04-24T09:29:59.445Z</t>
   </si>
   <si>
     <t>AstraZeneca condivide la sua solida early-science in oncologia con la comunità medica all’AACR 2017</t>
@@ -994,7 +994,7 @@
     <t>area-stampa/press-releases/2017/acalabrutinib</t>
   </si>
   <si>
-    <t>2026-04-05T20:56:16.383Z</t>
+    <t>2026-04-24T09:18:15.477Z</t>
   </si>
   <si>
     <t>Acalabrutinib di AstraZeneca approvato dall’FDA per i pazienti adulti con linfoma mantellare che hanno già ricevuto un trattamento</t>
@@ -1009,7 +1009,7 @@
     <t>area-stampa/press-releases/2017/benralizumab-zonda</t>
   </si>
   <si>
-    <t>2026-04-05T20:57:26.730Z</t>
+    <t>2026-04-24T09:26:29.777Z</t>
   </si>
   <si>
     <t>Il trial ZONDA di Fase III per benralizumab mostra la capacità di ridurre l’utilizzo di steroidi orali nei pazienti con asma grave</t>
@@ -1039,7 +1039,7 @@
     <t>area-stampa/press-releases/2017/brodalumab</t>
   </si>
   <si>
-    <t>2026-04-05T20:58:00.747Z</t>
+    <t>2026-04-24T09:36:56.009Z</t>
   </si>
   <si>
     <t>Brodalumab approvato dalla statunitense FDA per i pazienti adulti affetti da psoriasi a placche da moderata a grave</t>
@@ -1054,7 +1054,7 @@
     <t>area-stampa/press-releases/2017/budesonide-formoterolo-spray</t>
   </si>
   <si>
-    <t>2026-04-05T20:58:35.926Z</t>
+    <t>2026-04-24T09:20:39.840Z</t>
   </si>
   <si>
     <t>BPCO: disponibile in Italia la nuova formulazione spray di budesonide/formoterolo di AstraZeneca</t>
@@ -1069,7 +1069,7 @@
     <t>area-stampa/press-releases/2017/cambridge-nuovasede</t>
   </si>
   <si>
-    <t>2026-04-05T20:46:16.292Z</t>
+    <t>2026-04-24T09:28:50.094Z</t>
   </si>
   <si>
     <t>AstraZeneca raggiunge un obiettivo chiave con la posa dell'ultima pietra del nuovo centro R&amp;S globale e della sede centrale di Cambridge, Regno Unito</t>
@@ -1084,7 +1084,7 @@
     <t>area-stampa/press-releases/2017/circassia-patologierespiratorie</t>
   </si>
   <si>
-    <t>2026-04-05T20:46:51.979Z</t>
+    <t>2026-04-24T09:31:43.264Z</t>
   </si>
   <si>
     <t>AstraZeneca e Circassia avviano una collaborazione strategica per le patologie respiratorie</t>
@@ -1099,7 +1099,7 @@
     <t>area-stampa/press-releases/2017/cvd-real-sglt2</t>
   </si>
   <si>
-    <t>2026-04-06T04:13:41.004Z</t>
+    <t>2026-04-24T09:32:51.710Z</t>
   </si>
   <si>
     <t>Lo studio CVD-Real presentato all'ACC ha dimostrato che gli inibitori dell' SGLT-2 riducono significativamente l'ospedalizzazione per scompenso cardiaco e la mortalità</t>
@@ -1114,7 +1114,7 @@
     <t>area-stampa/press-releases/2017/dapagliflozin-ada</t>
   </si>
   <si>
-    <t>2026-04-05T20:59:11.286Z</t>
+    <t>2026-04-24T09:23:34.740Z</t>
   </si>
   <si>
     <t>In occasione dell’ADA 2017, AstraZeneca ha presentato nuovi dati a sostegno del profilo di sicurezza e degli outcomes cardiovascolari real-world di dapagliflozin</t>
@@ -1129,7 +1129,7 @@
     <t>area-stampa/press-releases/2017/diabete-dapagliflozin-saxagliptin</t>
   </si>
   <si>
-    <t>2026-04-05T20:59:47.046Z</t>
+    <t>2026-04-24T09:34:02.030Z</t>
   </si>
   <si>
     <t>L'FDA approva le compresse di dapagliflozin/saxagliptin da assumere una volta al giorno per gli adulti con diabete di tipo 2</t>
@@ -1144,7 +1144,7 @@
     <t>area-stampa/press-releases/2017/durvalumab-approvazionefda</t>
   </si>
   <si>
-    <t>2026-04-05T21:00:57.531Z</t>
+    <t>2026-04-24T09:28:15.320Z</t>
   </si>
   <si>
     <t>Durvalumab di AstraZeneca riceve approvazione accelerata dalla statunitense FDA per i pazienti con tumore della vescica in stadio avanzato precedentemente trattati con chemioterapia</t>
@@ -1159,13 +1159,13 @@
     <t>area-stampa/press-releases/2017/durvalumab-breakthrough-therapy-designation</t>
   </si>
   <si>
-    <t>2026-04-06T04:15:38.213Z</t>
+    <t>2026-04-24T07:40:50.761Z</t>
   </si>
   <si>
     <t>FDA: Breakthrough Therapy designation per durvalumab di AstraZeneca nel carcinoma polmonare non a piccole cellule localmente avanzato non operabile</t>
   </si>
   <si>
-    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/durvalumab_breakthrough therapy designation.html</t>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/durvalumab_breakthrough%20therapy%20designation.html</t>
   </si>
   <si>
     <t>area-stampa/press-releases/2017/durvalumab-ema.report.json</t>
@@ -1174,7 +1174,7 @@
     <t>area-stampa/press-releases/2017/durvalumab-ema</t>
   </si>
   <si>
-    <t>2026-04-05T20:47:27.346Z</t>
+    <t>2026-04-24T09:18:52.052Z</t>
   </si>
   <si>
     <t>L’EMA ha accettato la richiesta di autorizzazione all’immissione in commercio di durvalumab, prima immunoterapia per il carcinoma polmonare non a piccole cellule (NSCLC) localmente avanzato non resecabile</t>
@@ -1189,7 +1189,7 @@
     <t>area-stampa/press-releases/2017/durvalumab-studiopacific</t>
   </si>
   <si>
-    <t>2026-04-05T21:00:21.918Z</t>
+    <t>2026-04-24T09:27:40.734Z</t>
   </si>
   <si>
     <t>Durvalumab riduce significativamente il rischio di progressione della malattia o di morte nel trial di Fase III PACIFIC per il carcinoma polmonare non operabile in Stadio III</t>
@@ -1204,7 +1204,7 @@
     <t>area-stampa/press-releases/2017/exenatide-studioexscel</t>
   </si>
   <si>
-    <t>2026-04-05T21:02:07.816Z</t>
+    <t>2026-04-24T09:27:05.020Z</t>
   </si>
   <si>
     <t>Lo studio EXSCEL con exenatide ha raggiunto l’endopoint primario di sicurezza in pazienti con diabete di Tipo-2 che presentano diversi tipi di rischio cardiovascolare</t>
@@ -1219,7 +1219,7 @@
     <t>area-stampa/press-releases/2017/flaura-tumore-al-polmone1</t>
   </si>
   <si>
-    <t>2026-04-05T20:48:03.842Z</t>
+    <t>2026-04-24T09:21:14.653Z</t>
   </si>
   <si>
     <t>Osimertinib di AstraZeneca: potenziale nuovo standard terapeutico del carcinoma polmonare con EGFR mutato di prima linea</t>
@@ -1234,7 +1234,7 @@
     <t>area-stampa/press-releases/2017/globaldiabetespolicyforum</t>
   </si>
   <si>
-    <t>2026-04-05T20:48:38.557Z</t>
+    <t>2026-04-24T09:20:03.891Z</t>
   </si>
   <si>
     <t>A Roma il Global Diabetes Policy Forum: esperti nazionali e internazionali uniti per una corretta gestione del paziente</t>
@@ -1249,7 +1249,7 @@
     <t>area-stampa/press-releases/2017/goserelin</t>
   </si>
   <si>
-    <t>2026-04-05T21:02:43.667Z</t>
+    <t>2026-04-24T09:36:21.617Z</t>
   </si>
   <si>
     <t>AstraZeneca stipula un accordo con TerSera Therapeutics per Goserelin acetato negli USA e in Canada</t>
@@ -1264,7 +1264,7 @@
     <t>area-stampa/press-releases/2017/immunoncologia</t>
   </si>
   <si>
-    <t>2026-04-05T21:03:19.022Z</t>
+    <t>2026-04-24T09:38:41.606Z</t>
   </si>
   <si>
     <t>AstraZeneca amplia le opportunità del programma di immuno-oncologia per il carcinoma polmonare di prima linea</t>
@@ -1279,7 +1279,7 @@
     <t>area-stampa/press-releases/2017/linfoma-mantellare</t>
   </si>
   <si>
-    <t>2026-04-05T21:03:54.555Z</t>
+    <t>2026-04-24T09:23:00.362Z</t>
   </si>
   <si>
     <t>FDA: Breakthrough Therapy Designation e Priority Review per acalabrutinib di AstraZeneca per i pazienti con linfoma mantellare</t>
@@ -1294,7 +1294,7 @@
     <t>area-stampa/press-releases/2017/medimmune-sanofipasteur-medi8897</t>
   </si>
   <si>
-    <t>2026-04-05T20:49:14.967Z</t>
+    <t>2026-04-24T09:34:36.419Z</t>
   </si>
   <si>
     <t>MedImmune e Sanofi Pasteur formano un’alleanza per sviluppare e commercializzare il potenziale anticorpo di nuova generazione MEDI8897 contro il virus respiratorio sinciziale</t>
@@ -1309,7 +1309,7 @@
     <t>area-stampa/press-releases/2017/neuromieliteottica</t>
   </si>
   <si>
-    <t>2026-04-05T20:49:50.759Z</t>
+    <t>2026-04-24T09:31:09.100Z</t>
   </si>
   <si>
     <t>Il farmaco di AstraZeneca studiato per il disturbo dello spettro della neuromielite ottica riceve la designazione di farmaco orfano in Europa</t>
@@ -1324,7 +1324,7 @@
     <t>area-stampa/press-releases/2017/olaparib-brca-solo2</t>
   </si>
   <si>
-    <t>2026-04-05T20:50:25.322Z</t>
+    <t>2026-04-24T09:33:28.222Z</t>
   </si>
   <si>
     <t>I dati di fase III dello Studio SOLO-2 su olaparib in terapia di mantenimento dimostrano un vantaggio in termini di sopravvivenza libera da progressione nel carcinoma ovarico con mutazione BRCA</t>
@@ -1339,7 +1339,7 @@
     <t>area-stampa/press-releases/2017/olaparib-carcinomamammario-olympiad</t>
   </si>
   <si>
-    <t>2026-04-05T20:51:34.256Z</t>
+    <t>2026-04-24T09:25:55.368Z</t>
   </si>
   <si>
     <t>Olaparib riduce significativamente il rischio di progressione della malattia o di morte nelle pazienti con carcinoma mammario metastatico BRCA mutato</t>
@@ -1354,7 +1354,7 @@
     <t>area-stampa/press-releases/2017/olaparib-olympiad</t>
   </si>
   <si>
-    <t>2026-04-05T20:51:00.469Z</t>
+    <t>2026-04-24T09:35:10.577Z</t>
   </si>
   <si>
     <t>Olaparib aumenta la sopravvivenza nelle pazienti affette da tumore al seno metastatico positivo alla mutazione BRCA</t>
@@ -1369,7 +1369,7 @@
     <t>area-stampa/press-releases/2017/olaparib-tumoreovarico-studiosolo2</t>
   </si>
   <si>
-    <t>2026-04-05T20:52:10.152Z</t>
+    <t>2026-04-24T09:24:09.317Z</t>
   </si>
   <si>
     <t>La terapia di mantenimento con olaparib nelle donne con tumore ovarico BRCA mutato preserva la qualità di vita oltre ad aumentare la sopravvivenza libera da progressione</t>
@@ -1384,7 +1384,7 @@
     <t>area-stampa/press-releases/2017/osimertinib-btd</t>
   </si>
   <si>
-    <t>2026-04-05T20:52:45.176Z</t>
+    <t>2026-04-24T09:19:27.387Z</t>
   </si>
   <si>
     <t>Osimertinib ottiene dall’FDA la breakthrough therapy designation per il trattamento in prima linea dei pazienti affetti da carcinoma polmonare non a piccole cellule positivo alla mutazione dell’EGFR</t>
@@ -1399,7 +1399,7 @@
     <t>area-stampa/press-releases/2017/osimertinib-cfda</t>
   </si>
   <si>
-    <t>2026-04-05T21:05:06.166Z</t>
+    <t>2026-04-24T09:30:34.105Z</t>
   </si>
   <si>
     <t>Osimertinib approvato in Cina come primo trattamento per il carcinoma polmonare non a piccole cellule metastatico positivo alla mutazione T790M del recettore EGFR</t>
@@ -1414,7 +1414,7 @@
     <t>area-stampa/press-releases/2017/osimertinib-fdausa</t>
   </si>
   <si>
-    <t>2026-04-05T21:04:29.851Z</t>
+    <t>2026-04-24T09:29:25.244Z</t>
   </si>
   <si>
     <t>Osimertinib riceve piena approvazione da parte della statunitense Food and Drug Administration (FDA)</t>
@@ -1429,7 +1429,7 @@
     <t>area-stampa/press-releases/2017/osimertinib-rimborsabile</t>
   </si>
   <si>
-    <t>2026-04-05T21:05:39.900Z</t>
+    <t>2026-04-24T09:22:25.546Z</t>
   </si>
   <si>
     <t>Carcinoma polmonare: osimertinib ottiene la rimborsabilità</t>
@@ -1444,7 +1444,7 @@
     <t>area-stampa/press-releases/2017/osimertinib-tumorealpolmone-aura3</t>
   </si>
   <si>
-    <t>2026-04-05T21:06:14.934Z</t>
+    <t>2026-04-24T09:24:45.633Z</t>
   </si>
   <si>
     <t>AstraZeneca presenta i dati di osimertinib nei pazienti con tumore al polmone positivo alla mutazione T790 dell'EGFR e metastasi al sistema nervoso centrale</t>
@@ -1459,7 +1459,7 @@
     <t>area-stampa/press-releases/2017/pacific-tumore-al-polmone</t>
   </si>
   <si>
-    <t>2026-04-05T20:53:21.823Z</t>
+    <t>2026-04-24T09:21:50.260Z</t>
   </si>
   <si>
     <t>Durvalumab di AstraZeneca, prima terapia immuno-oncologica a dimostrare una sopravvivenza libera da progressione superiore rispetto alla terapia standard per i pazienti affetti da carcinoma polmonare in stadio III localmente avanzato</t>
@@ -1474,13 +1474,13 @@
     <t>area-stampa/press-releases/2017/patient-advocacy-network</t>
   </si>
   <si>
-    <t>2026-04-06T04:15:02.690Z</t>
+    <t>2026-04-24T07:40:15.844Z</t>
   </si>
   <si>
     <t>Associazioni pazienti sempre più preparate per un ruolo attivo nel governo del sistema sanitario: al via la terza edizione del Patient Advocacy Network</t>
   </si>
   <si>
-    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Patient Advocacy Network.html</t>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2017/Patient%20Advocacy%20Network.html</t>
   </si>
   <si>
     <t>area-stampa/press-releases/2017/topemployers2017.report.json</t>
@@ -1489,7 +1489,7 @@
     <t>area-stampa/press-releases/2017/topemployers2017</t>
   </si>
   <si>
-    <t>2026-04-05T20:54:31.443Z</t>
+    <t>2026-04-24T09:37:31.796Z</t>
   </si>
   <si>
     <t>AstraZeneca è Top Employer 2017</t>
@@ -1504,7 +1504,7 @@
     <t>area-stampa/press-releases/2017/zs-9-iperkaliemia</t>
   </si>
   <si>
-    <t>2026-04-05T20:55:07.201Z</t>
+    <t>2026-04-24T09:32:17.473Z</t>
   </si>
   <si>
     <t>AstraZeneca riceve una Complete Response Letter dalla FDA per ZS-9 per il trattamento dell’iperkaliemia</t>
@@ -1519,7 +1519,7 @@
     <t>area-stampa/press-releases/2017/zs9-iperkaliemia-zspharma</t>
   </si>
   <si>
-    <t>2026-04-05T20:55:41.189Z</t>
+    <t>2026-04-24T09:35:45.450Z</t>
   </si>
   <si>
     <t>ZS-9 riceve il parere positivo del CHMP per il trattamento dell’iperkaliemia</t>
@@ -1569,7 +1569,7 @@
     <t>area-stampa/press-releases/2018/aa</t>
   </si>
   <si>
-    <t>2026-04-05T21:06:48.808Z</t>
+    <t>2026-04-24T09:05:44.797Z</t>
   </si>
   <si>
     <t>Lo studio di fase III THEMIS raggiunge il suo endpoint primario e conferma che ticagrelor riduce gli eventi cardiovascolari in pazienti affetti da diabete e malattia coronarica</t>
@@ -1587,7 +1587,7 @@
     <t>area-stampa/press-releases/2018/acalabrutinib-elevatetn-ash</t>
   </si>
   <si>
-    <t>2026-04-05T21:07:25.020Z</t>
+    <t>2026-04-24T08:52:50.789Z</t>
   </si>
   <si>
     <t>Leucemia linfatica cronica: acalabrutinib migliora significativamente il tempo libero da progressione o morte nei pazienti non precedentemente trattati</t>
@@ -1617,7 +1617,7 @@
     <t>area-stampa/press-releases/2018/acalabrutinib-llc-ascend</t>
   </si>
   <si>
-    <t>2026-04-05T21:08:36.611Z</t>
+    <t>2026-04-24T09:00:29.657Z</t>
   </si>
   <si>
     <t>Leucemia linfatica cronica: acalabrutinib migliora significativamente il tempo libero da progressione nei pazienti recidivanti o refrattari</t>
@@ -1647,7 +1647,7 @@
     <t>area-stampa/press-releases/2018/aha-2018</t>
   </si>
   <si>
-    <t>2026-04-05T21:09:46.321Z</t>
+    <t>2026-04-24T09:06:18.518Z</t>
   </si>
   <si>
     <t>Dapagliflozin riduce significativamente le ospedalizzazioni dovute a scompenso cardiaco o morte cardiovascolare in una vasta popolazione di pazienti affetti da diabete di tipo 2</t>
@@ -1677,7 +1677,7 @@
     <t>area-stampa/press-releases/2018/astrazeneca-covid-19</t>
   </si>
   <si>
-    <t>2026-04-05T21:10:55.644Z</t>
+    <t>2026-04-24T08:51:06.846Z</t>
   </si>
   <si>
     <t>AstraZeneca a supporto di medici e personale sanitario in prima linea nell’emergenza COVID-19, oggi e domani</t>
@@ -1692,7 +1692,7 @@
     <t>area-stampa/press-releases/2018/astrazeneca-top-employers-2020</t>
   </si>
   <si>
-    <t>2026-04-05T21:12:06.823Z</t>
+    <t>2026-04-24T08:51:41.194Z</t>
   </si>
   <si>
     <t>AstraZeneca è Top Employers Italia e Top Employers Europe 2020</t>
@@ -1722,7 +1722,7 @@
     <t>area-stampa/press-releases/2018/astrazeneca-vaccino-covid-19</t>
   </si>
   <si>
-    <t>2026-04-05T21:12:42.147Z</t>
+    <t>2026-04-24T08:46:25.680Z</t>
   </si>
   <si>
     <t>Il vaccino AZD1222 per il COVID-19 ha prodotto importanti risposte immunitarie su tutti i partecipanti dello studio clinico di fase I/II</t>
@@ -1737,7 +1737,7 @@
     <t>area-stampa/press-releases/2018/astrazeneca-vaccino-covid19</t>
   </si>
   <si>
-    <t>2026-04-05T21:13:17.267Z</t>
+    <t>2026-04-24T08:48:11.207Z</t>
   </si>
   <si>
     <t>AstraZeneca fornirà ai Paesi europei fino a 400 milioni di dosi del vaccino della Oxford University</t>
@@ -1752,7 +1752,7 @@
     <t>area-stampa/press-releases/2018/benralizumab-bora-ers</t>
   </si>
   <si>
-    <t>2026-04-05T21:15:39.705Z</t>
+    <t>2026-04-24T09:08:38.715Z</t>
   </si>
   <si>
     <t>Asma grave eosinofilico. Benralizumab, nello studio di fase III BORA, dimostra un profilo di sicurezza ed efficacia mantenuto nel lungo termine</t>
@@ -1767,7 +1767,7 @@
     <t>area-stampa/press-releases/2018/benralizumab-chmp-autosomministrazione</t>
   </si>
   <si>
-    <t>2026-04-05T21:13:52.388Z</t>
+    <t>2026-04-24T08:59:19.474Z</t>
   </si>
   <si>
     <t>Asma grave eosinofilico - Parere positivo del CHMP per il trattamento tramite auto-somministrazione di benralizumab e per l’utilizzo del nuovo dispositivo auto-iniettore pre-riempito monouso</t>
@@ -1782,7 +1782,7 @@
     <t>area-stampa/press-releases/2018/benralizumab-ponente</t>
   </si>
   <si>
-    <t>2026-04-05T21:14:27.518Z</t>
+    <t>2026-04-24T08:42:16.155Z</t>
   </si>
   <si>
     <t>ASMA GRAVE EOSINOFILICO – Dati dello studio di fase IIIb PONENTE mostrano che benralizumab elimina la necessità di ricorrere ai corticosteroidi orali nella maggior parte dei pazienti asmatici gravi</t>
@@ -1797,7 +1797,7 @@
     <t>area-stampa/press-releases/2018/benralizumabema</t>
   </si>
   <si>
-    <t>2026-04-06T04:17:59.145Z</t>
+    <t>2026-04-24T09:17:40.988Z</t>
   </si>
   <si>
     <t>Approvazione EMA per benralizumab di AstraZeneca nel trattamento dell’asma grave eosinofilico</t>
@@ -1812,7 +1812,7 @@
     <t>area-stampa/press-releases/2018/budesonide-glicopirronio-formoterolo-ethos-bpco</t>
   </si>
   <si>
-    <t>2026-04-05T21:15:03.578Z</t>
+    <t>2026-04-24T08:47:37.213Z</t>
   </si>
   <si>
     <t>Lo studio di Fase III ETHOS dimostra che la triplice terapia budesonide-glicopirronio-formoterolo fumarato riduce significativamente il tasso di riacutizzazioni moderate o severe in pazienti affetti da BPCO</t>
@@ -1827,7 +1827,7 @@
     <t>area-stampa/press-releases/2018/campagnaioscelgodisapere</t>
   </si>
   <si>
-    <t>2026-04-05T01:14:24.606Z</t>
+    <t>2026-04-24T09:14:44.968Z</t>
   </si>
   <si>
     <t>Seconda edizione di “Io scelgo di sapere”, la campagna di informazione sul tumore ovarico e ereditario e sul test genetico BRCA</t>
@@ -1842,7 +1842,7 @@
     <t>area-stampa/press-releases/2018/dapagliflozin-chmp-declare-cvdata</t>
   </si>
   <si>
-    <t>2026-04-05T21:16:14.597Z</t>
+    <t>2026-04-24T08:58:08.659Z</t>
   </si>
   <si>
     <t>Diabete di tipo 2 – Parere positivo del CHMP per l'aggiornamento delle indicazioni di dapagliflozin: inclusi i dati di outcome cardio-renali dello studio DECLARE-TIMI 58</t>
@@ -1857,7 +1857,7 @@
     <t>area-stampa/press-releases/2018/dapagliflozin-dapa-ckd-esc</t>
   </si>
   <si>
-    <t>2026-04-05T21:16:50.174Z</t>
+    <t>2026-04-24T08:45:50.062Z</t>
   </si>
   <si>
     <t>Studio di Fase III DAPA-CKD: dapagliflozin ha dimostrato una riduzione senza precedenti del rischio di insufficienza renale e di morte per causa cardiovascolare o renale in pazienti affetti da malattia renale cronica</t>
@@ -1872,7 +1872,7 @@
     <t>area-stampa/press-releases/2018/dapagliflozin-dapa-hf-esc2019</t>
   </si>
   <si>
-    <t>2026-04-05T21:17:25.038Z</t>
+    <t>2026-04-24T08:55:47.776Z</t>
   </si>
   <si>
     <t>Presentati a ESC 2019 i risultati dello studio di FASE III DAPA-HF che hanno mostrato come dapagliflozin abbia significativamente ridotto l’incidenza di morte per causa cardiovascolare e il peggioramento dello scompenso cardiaco</t>
@@ -1887,7 +1887,7 @@
     <t>area-stampa/press-releases/2018/dapagliflozin-dapackd-acc</t>
   </si>
   <si>
-    <t>2026-04-05T21:18:00.550Z</t>
+    <t>2026-04-24T08:50:32.441Z</t>
   </si>
   <si>
     <t>Malattia renale cronica - Studio di Fase III DAPA-CKD interrotto in anticipo per conclamata efficacia di dapaglifozin sui pazienti</t>
@@ -1902,7 +1902,7 @@
     <t>area-stampa/press-releases/2018/dapagliflozin-declare-renaldata</t>
   </si>
   <si>
-    <t>2026-04-05T21:18:34.992Z</t>
+    <t>2026-04-24T09:01:39.789Z</t>
   </si>
   <si>
     <t>Lo studio di dapagliflozin ha mostrato la riduzione della progressione della malattia renale o della morte renale nei pazienti con diabete di tipo 2</t>
@@ -1917,7 +1917,7 @@
     <t>area-stampa/press-releases/2018/dapagliflozin-hf-approvazioneeu</t>
   </si>
   <si>
-    <t>2026-04-05T21:19:09.267Z</t>
+    <t>2026-04-24T08:41:40.966Z</t>
   </si>
   <si>
     <t>Dapagliflozin approvato in Europa per il trattamento dello scompenso cardiaco</t>
@@ -1932,7 +1932,7 @@
     <t>area-stampa/press-releases/2018/dapaglifozin-declare-top-line</t>
   </si>
   <si>
-    <t>2026-04-06T04:16:13.436Z</t>
+    <t>2026-04-24T10:08:48.617Z</t>
   </si>
   <si>
     <t>Dapagliflozin ha ottenuto risultati positivi nello studio di fase III DECLARE-TIMI 58, un ampio studio condotto sugli outcomes cardiovascolari che ha coinvolto 17.000 pazienti con diabete di tipo 2</t>
@@ -1947,7 +1947,7 @@
     <t>area-stampa/press-releases/2018/declaresottoanalisi</t>
   </si>
   <si>
-    <t>2026-04-05T21:19:43.948Z</t>
+    <t>2026-04-24T09:05:08.489Z</t>
   </si>
   <si>
     <t>Risultati positivi dalla prime sotto-analisi dello studio di Fase III DECLARE-TIMI 58.</t>
@@ -1962,7 +1962,7 @@
     <t>area-stampa/press-releases/2018/durvalumab-caspian-iaslc</t>
   </si>
   <si>
-    <t>2026-04-05T21:20:20.256Z</t>
+    <t>2026-04-24T08:55:12.263Z</t>
   </si>
   <si>
     <t>Tumore del polmone: durvalumab dimostra un significativo beneficio in termini di sopravvivenza e un miglioramento nel numero e nella durata delle risposte nel trattamento del carcinoma a piccole cellule in stadio avanzato</t>
@@ -1977,7 +1977,7 @@
     <t>area-stampa/press-releases/2018/durvalumab-caspian-sclc-asco</t>
   </si>
   <si>
-    <t>2026-04-05T21:20:55.791Z</t>
+    <t>2026-04-24T08:49:21.104Z</t>
   </si>
   <si>
     <t>Tumore del polmone a piccole cellule. Durvalumab conferma un beneficio sostenuto di sopravvivenza globale quale trattamento di prima linea dei pazienti affetti da malattia estesa</t>
@@ -1992,7 +1992,7 @@
     <t>area-stampa/press-releases/2018/durvalumab-ok-ue-sclc</t>
   </si>
   <si>
-    <t>2026-04-05T21:21:30.157Z</t>
+    <t>2026-04-24T08:45:14.845Z</t>
   </si>
   <si>
     <t>Tumore del polmone a piccole cellule - Ok della Commissione Europea per durvalumab nel trattamento della malattia estesa</t>
@@ -2007,7 +2007,7 @@
     <t>area-stampa/press-releases/2018/durvalumab-pacific-esmo</t>
   </si>
   <si>
-    <t>2026-04-05T21:22:04.753Z</t>
+    <t>2026-04-24T08:43:27.077Z</t>
   </si>
   <si>
     <t>Carcinoma polmonare non a piccole cellule in stadio III non resecabile - Durvalumab mostra un beneficio di sopravvivenza a 4 anni senza precedenti per i pazienti in questo setting, per i quali si prospetta una possibilità di guarigione</t>
@@ -2022,7 +2022,7 @@
     <t>area-stampa/press-releases/2018/durvalumab-parerepositivochmp</t>
   </si>
   <si>
-    <t>2026-04-05T21:23:50.737Z</t>
+    <t>2026-04-24T09:10:24.083Z</t>
   </si>
   <si>
     <t>Parere positivo del CHMP per durvalumab nel carcinoma polmonare non a piccole cellule (NSCLC) localmente avanzato, non resecabile</t>
@@ -2037,7 +2037,7 @@
     <t>area-stampa/press-releases/2018/durvalumab-tumorepolmone</t>
   </si>
   <si>
-    <t>2026-04-05T21:22:39.325Z</t>
+    <t>2026-04-24T09:02:13.682Z</t>
   </si>
   <si>
     <t>Durvalumab, unica immunoterapia con sopravvivenza globale a tre anni nel tumore del polmone non a piccole cellule in stadio III non operabile</t>
@@ -2052,7 +2052,7 @@
     <t>area-stampa/press-releases/2018/durvalumab</t>
   </si>
   <si>
-    <t>2026-04-06T04:18:34.429Z</t>
+    <t>2026-04-24T09:15:54.710Z</t>
   </si>
   <si>
     <t>FDA approva durvalumab per il trattamento del tumore al polmone non a piccole cellule al III Stadio non resecabile</t>
@@ -2067,7 +2067,7 @@
     <t>area-stampa/press-releases/2018/durvalumabpacificos</t>
   </si>
   <si>
-    <t>2026-04-05T01:15:35.100Z</t>
+    <t>2026-04-24T09:13:01.048Z</t>
   </si>
   <si>
     <t>Durvalumab migliora significativamente la sopravvivenza globale nei pazienti con carcinoma polmonare non a piccole cellule in stadio III non operabile che hanno ancora possibilità di guarigione</t>
@@ -2082,7 +2082,7 @@
     <t>area-stampa/press-releases/2018/hlr-flaura-os</t>
   </si>
   <si>
-    <t>2026-04-05T21:24:25.055Z</t>
+    <t>2026-04-24T08:56:59.837Z</t>
   </si>
   <si>
     <t>Tumore del polmone: osimertinib in prima linea migliora significativamente la sopravvivenza globale</t>
@@ -2097,7 +2097,7 @@
     <t>area-stampa/press-releases/2018/lung-ambition-alliance</t>
   </si>
   <si>
-    <t>2026-04-05T21:24:59.751Z</t>
+    <t>2026-04-24T08:57:33.581Z</t>
   </si>
   <si>
     <t>Tumore del polmone: nasce la Lung Ambition Alliance. L’obiettivo è raddoppiare la sopravvivenza a 5 anni entro il 2025</t>
@@ -2112,7 +2112,7 @@
     <t>area-stampa/press-releases/2018/nomina-chiara-gargiulo-vp-ria</t>
   </si>
   <si>
-    <t>2026-04-05T21:29:36.334Z</t>
+    <t>2026-04-24T09:09:14.125Z</t>
   </si>
   <si>
     <t>Chiara Gargiulo è il nuovo Vice President della Business Unit Respiratory, Inflammation e Autoimmunity di AstraZeneca Italia</t>
@@ -2127,7 +2127,7 @@
     <t>area-stampa/press-releases/2018/nomina-driol-hr</t>
   </si>
   <si>
-    <t>2026-04-05T21:25:34.731Z</t>
+    <t>2026-04-24T08:58:43.334Z</t>
   </si>
   <si>
     <t>Tamara Driol alla Direzione delle Risorse Umane di AstraZeneca Italia</t>
@@ -2142,7 +2142,7 @@
     <t>area-stampa/press-releases/2018/nomina-mirkomerletti</t>
   </si>
   <si>
-    <t>2026-04-05T21:26:09.238Z</t>
+    <t>2026-04-24T08:49:57.545Z</t>
   </si>
   <si>
     <t>Mirko Merletti nuovo Vice President della Business Unit Oncology di AstraZeneca Italia</t>
@@ -2157,7 +2157,7 @@
     <t>area-stampa/press-releases/2018/nomina-oliveros-medicalhead</t>
   </si>
   <si>
-    <t>2026-04-05T21:26:43.467Z</t>
+    <t>2026-04-24T09:01:04.215Z</t>
   </si>
   <si>
     <t>Constanza Oliveros nuovo Direttore Medico di AstraZeneca Italia</t>
@@ -2172,7 +2172,7 @@
     <t>area-stampa/press-releases/2018/nomina-scott-pescatore-vp-obu</t>
   </si>
   <si>
-    <t>2026-04-05T21:30:12.750Z</t>
+    <t>2026-04-24T09:09:48.989Z</t>
   </si>
   <si>
     <t>Scott Pescatore nuovo Vice President della Business Unit Oncology di AstraZeneca Italia</t>
@@ -2187,7 +2187,7 @@
     <t>area-stampa/press-releases/2018/notastampa-dati-inglesi-rwe</t>
   </si>
   <si>
-    <t>2026-04-05T21:28:27.912Z</t>
+    <t>2026-04-24T08:38:10.825Z</t>
   </si>
   <si>
     <t>Studio inglese su dati di real world evidence (RWE) conferma l’efficacia del vaccino AstraZeneca nel prevenire tutti i livelli di gravità della malattia negli over 70</t>
@@ -2202,7 +2202,7 @@
     <t>area-stampa/press-releases/2018/notastampaconsegnevaccino</t>
   </si>
   <si>
-    <t>2026-04-05T21:27:17.821Z</t>
+    <t>2026-04-24T08:38:44.663Z</t>
   </si>
   <si>
     <t>Dichiarazione di AstraZeneca in merito al ritardo delle consegne</t>
@@ -2217,7 +2217,7 @@
     <t>area-stampa/press-releases/2018/notastampaestraneitavenditamercatiparalleli</t>
   </si>
   <si>
-    <t>2026-04-05T21:27:52.378Z</t>
+    <t>2026-04-24T08:39:20.132Z</t>
   </si>
   <si>
     <t>Dichiarazione di AstraZeneca in merito all'estraneità alla vendita del vaccino su mercati paralleli</t>
@@ -2232,7 +2232,7 @@
     <t>area-stampa/press-releases/2018/novelstart</t>
   </si>
   <si>
-    <t>2026-04-05T21:29:02.491Z</t>
+    <t>2026-04-24T09:03:23.487Z</t>
   </si>
   <si>
     <t>Asma lieve - Nuovi dati mostrano l’efficacia della combinazione budesonide/formoterolo nella riduzione degli attacchi di asma lieve rispetto alla terapia comunemente più utilizzata</t>
@@ -2247,7 +2247,7 @@
     <t>area-stampa/press-releases/2018/olaparib-ovaio-soloi-approvazioneeu</t>
   </si>
   <si>
-    <t>2026-04-05T21:30:47.953Z</t>
+    <t>2026-04-24T08:59:54.899Z</t>
   </si>
   <si>
     <t>Carcinoma ovarico avanzato: olaparib approvato in Europa per il trattamento in prima linea delle pazienti con mutazione BRCA</t>
@@ -2259,7 +2259,7 @@
     <t>area-stampa/press-releases/2018/olaparib-paola-esmo2019</t>
   </si>
   <si>
-    <t>2026-04-05T20:33:40.254Z</t>
+    <t>2026-04-24T08:54:01.387Z</t>
   </si>
   <si>
     <t>Olaparib in associazione a bevacizumab aumenta significativamente il tempo libero da progressione nel trattamento di prima linea del tumore ovarico avanzato di nuova diagnosi</t>
@@ -2274,7 +2274,7 @@
     <t>area-stampa/press-releases/2018/olaparib-paolai-approvazioneeu</t>
   </si>
   <si>
-    <t>2026-04-05T20:33:04.874Z</t>
+    <t>2026-04-24T08:41:05.444Z</t>
   </si>
   <si>
     <t>Carcinoma ovarico avanzato: ok della Commissione Europea per olaparib in combinazione con bevacizumab per il trattamento di mantenimento in prima linea delle pazienti HRD-positive</t>
@@ -2289,7 +2289,7 @@
     <t>area-stampa/press-releases/2018/olaparib-profound-esmo</t>
   </si>
   <si>
-    <t>2026-04-05T13:21:20.673Z</t>
+    <t>2026-04-24T08:42:51.380Z</t>
   </si>
   <si>
     <t>Tumore della prostata: olaparib riduce il rischio di morte del 31% nei pazienti con malattia metastatica resistente alla castrazione e mutazione BRCA1/2 o ATM</t>
@@ -2301,7 +2301,7 @@
     <t>area-stampa/press-releases/2018/olaparib-profound-prostata-esmo2019</t>
   </si>
   <si>
-    <t>2026-04-05T13:21:57.088Z</t>
+    <t>2026-04-24T08:53:25.906Z</t>
   </si>
   <si>
     <t>Olaparib ha più che raddoppiato la sopravvivenza libera da progressione radiografica in pazienti con tumore della prostata metastatico resistente alla castrazione con mutazione BRCA1/2 o ATM (7,4 mesi rispetto a 3,6 dello standard di cura)</t>
@@ -2316,7 +2316,7 @@
     <t>area-stampa/press-releases/2018/olaparib-profund-approvazioneeu</t>
   </si>
   <si>
-    <t>2026-04-05T01:09:10.698Z</t>
+    <t>2026-04-24T08:40:29.660Z</t>
   </si>
   <si>
     <t>Tumore della prostata: ok della Commissione Europea per olaparib nel trattamento della malattia metastatica resistente alla castrazione con mutazione BRCA1/2</t>
@@ -2331,7 +2331,7 @@
     <t>area-stampa/press-releases/2018/olaparib-psp-az-msd</t>
   </si>
   <si>
-    <t>2026-04-05T01:09:44.928Z</t>
+    <t>2026-04-24T08:47:01.446Z</t>
   </si>
   <si>
     <t>Tumore dell’ovaio: dalla diagnosi al follow up, al via il programma CORE: Carcinoma Ovarico REmote Care per il supporto a domicilio delle pazienti durante l’emergenza covid-19 e oltre</t>
@@ -2346,7 +2346,7 @@
     <t>area-stampa/press-releases/2018/olaparib-seno-ovaio-rimborsabilita</t>
   </si>
   <si>
-    <t>2026-04-05T01:10:20.668Z</t>
+    <t>2026-04-24T08:39:54.649Z</t>
   </si>
   <si>
     <t>Tumori del seno e dell’ovaio: svolta nel trattamento delle forme legate alla mutazione del gene BRCA. Olaparib da oggi disponibile nelle due neoplasie</t>
@@ -2361,7 +2361,7 @@
     <t>area-stampa/press-releases/2018/olaparib-solo-1-esmo</t>
   </si>
   <si>
-    <t>2026-04-05T13:22:31.144Z</t>
+    <t>2026-04-24T08:44:03.428Z</t>
   </si>
   <si>
     <t>Carcinoma ovarico avanzato: olaparib in prima linea ritarda di oltre 4 anni e mezzo la progressione della malattia per le pazienti con mutazione BRCA</t>
@@ -2376,7 +2376,7 @@
     <t>area-stampa/press-releases/2018/olaparib-tumorepancreas</t>
   </si>
   <si>
-    <t>2026-04-05T01:10:54.964Z</t>
+    <t>2026-04-24T09:02:49.161Z</t>
   </si>
   <si>
     <t>Tumore del pancreas: “Olaparib ha quasi raddoppiato il tempo di sopravvivenza senza progressione della malattia nei pazienti BRCA mutati”</t>
@@ -2391,7 +2391,7 @@
     <t>area-stampa/press-releases/2018/osimertinib-eu</t>
   </si>
   <si>
-    <t>2026-04-06T04:16:47.598Z</t>
+    <t>2026-04-24T09:12:26.163Z</t>
   </si>
   <si>
     <t>Approvazione europea per osimertinib in prima linea per i pazienti affetti da carcinoma polmonare non a piccole cellule (NSCLC) con mutazione di EGFR</t>
@@ -2406,7 +2406,7 @@
     <t>area-stampa/press-releases/2018/osimertinib-flaura-esmo2019</t>
   </si>
   <si>
-    <t>2026-04-05T03:16:20.900Z</t>
+    <t>2026-04-24T08:54:38.082Z</t>
   </si>
   <si>
     <t>Osimertinib: l'unico EGFR TKI ad aver dimostrato una sopravvivenza mediana superiore a 3 anni</t>
@@ -2421,7 +2421,7 @@
     <t>area-stampa/press-releases/2018/osimertinib-nsclc-adaura-asco</t>
   </si>
   <si>
-    <t>2026-04-05T13:23:06.326Z</t>
+    <t>2026-04-24T08:48:46.744Z</t>
   </si>
   <si>
     <t>Tumore del polmone non a piccole cellule: osimertinib dimostra un risultato senza precedenti come terapia adiuvante in pazienti in stadio IB-IIIA positivi alla mutazione di EGFR</t>
@@ -2436,7 +2436,7 @@
     <t>area-stampa/press-releases/2018/osimertinib-rimborsabilita-1linea</t>
   </si>
   <si>
-    <t>2026-04-05T01:11:28.625Z</t>
+    <t>2026-04-24T08:52:16.396Z</t>
   </si>
   <si>
     <t>Tumore del polmone non a piccole cellule avanzato: osimertinib disponibile in Italia per il trattamento in prima linea dei pazienti con mutazione di EGFR</t>
@@ -2451,7 +2451,7 @@
     <t>area-stampa/press-releases/2018/osimertinib-tumorealpolmone-aura3</t>
   </si>
   <si>
-    <t>2026-04-06T04:19:11.359Z</t>
+    <t>2026-04-24T09:25:19.654Z</t>
   </si>
   <si>
     <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/osimertinib_tumorealpolmone_AURA3.html</t>
@@ -2463,7 +2463,7 @@
     <t>area-stampa/press-releases/2018/pacific-os-wclc</t>
   </si>
   <si>
-    <t>2026-04-05T01:12:37.248Z</t>
+    <t>2026-04-24T09:07:28.550Z</t>
   </si>
   <si>
     <t>Durvalumab è la prima immunoterapia che dimostra un beneficio significativo in sopravvivenza globale nel tumore del polmone in stadio III, non resecabile</t>
@@ -2478,7 +2478,7 @@
     <t>area-stampa/press-releases/2018/patientadvocacynetwork</t>
   </si>
   <si>
-    <t>2026-04-05T03:16:55.675Z</t>
+    <t>2026-04-24T09:03:58.844Z</t>
   </si>
   <si>
     <t>A Roma la quinta edizione del Patient Advocacy Network, organizzato da ALTEMS-Università Cattolica</t>
@@ -2493,7 +2493,7 @@
     <t>area-stampa/press-releases/2018/patientadvocacynetwork2018</t>
   </si>
   <si>
-    <t>2026-04-05T01:16:46.252Z</t>
+    <t>2026-04-24T09:14:08.921Z</t>
   </si>
   <si>
     <t>Associazioni di pazienti sempre più preparate e coinvolte nel governo del sistema sanitario: al via la quarta edizione del Patient Advocacy Network</t>
@@ -2508,7 +2508,7 @@
     <t>area-stampa/press-releases/2018/pennabenralizumab-disponibilitaitalia</t>
   </si>
   <si>
-    <t>2026-04-05T01:13:13.708Z</t>
+    <t>2026-04-24T08:44:39.022Z</t>
   </si>
   <si>
     <t>Asma grave eosinofilico - Approvata e disponibile in Italia la ‘penna’ per l’autosomministrazione di benralizumab</t>
@@ -2523,7 +2523,7 @@
     <t>area-stampa/press-releases/2018/senometastatico</t>
   </si>
   <si>
-    <t>2026-04-05T03:32:46.395Z</t>
+    <t>2026-04-24T09:04:34.668Z</t>
   </si>
   <si>
     <t>Tumore alla mammella: ok della Commissione Europea per olaparip nella malattia avanzata HER2-negativa con mutazione BRCA</t>
@@ -2538,7 +2538,7 @@
     <t>area-stampa/press-releases/2018/solo1-esmo2018</t>
   </si>
   <si>
-    <t>2026-04-05T03:17:30.795Z</t>
+    <t>2026-04-24T09:06:52.809Z</t>
   </si>
   <si>
     <t>Carcinoma ovarico: olaparib in prima linea riduce il rischio di progressione o morte del 70%</t>
@@ -2553,7 +2553,7 @@
     <t>area-stampa/press-releases/2018/solo1-olaparib</t>
   </si>
   <si>
-    <t>2026-04-06T04:17:23.081Z</t>
+    <t>2026-04-24T09:10:58.642Z</t>
   </si>
   <si>
     <t>Carcinoma ovarico: olaparib in prima linea ritarda in modo significativo la progressione della malattia</t>
@@ -2568,7 +2568,7 @@
     <t>area-stampa/press-releases/2018/studiocvdreal</t>
   </si>
   <si>
-    <t>2026-04-06T04:20:31.830Z</t>
+    <t>2026-04-24T09:15:19.705Z</t>
   </si>
   <si>
     <t>Nuovi dati dallo studio CVD-REAL su pazienti con diabete di tipo 2 a conferma dei benefici cardiovascolari associati all’uso degli inibitori SGLT-2</t>
@@ -2583,7 +2583,7 @@
     <t>area-stampa/press-releases/2018/ticagrelor-themis-esc2019</t>
   </si>
   <si>
-    <t>2026-04-05T01:13:49.140Z</t>
+    <t>2026-04-24T08:56:23.593Z</t>
   </si>
   <si>
     <t>ESC 2019 - Lo studio di fase III THEMIS ha confermato che ticagrelor riduce il rischio di eventi cardiovascolari nei pazienti affetti da malattia coronarica e diabete di tipo 2</t>
@@ -2598,7 +2598,7 @@
     <t>area-stampa/press-releases/2018/ticagrelor</t>
   </si>
   <si>
-    <t>2026-04-06T04:21:06.840Z</t>
+    <t>2026-04-24T09:16:31.439Z</t>
   </si>
   <si>
     <t>Ticagrelor 60 mg riduce significativamente gli eventi cardiovascolari e la mortalità oltre l’anno nei pazienti che hanno avuto un attacco cardiaco e che presentano coronaropatia multivasale</t>
@@ -2613,7 +2613,7 @@
     <t>area-stampa/press-releases/2018/topemployers2017</t>
   </si>
   <si>
-    <t>2026-04-05T03:18:41.533Z</t>
+    <t>2026-04-24T09:38:06.457Z</t>
   </si>
   <si>
     <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/TopEmployers2017.html</t>
@@ -2625,7 +2625,7 @@
     <t>area-stampa/press-releases/2018/topemployers2018</t>
   </si>
   <si>
-    <t>2026-04-06T04:21:40.796Z</t>
+    <t>2026-04-24T09:17:06.489Z</t>
   </si>
   <si>
     <t>AstraZeneca è Top Employers Italia e Top Employers Europe 2018</t>
@@ -2640,13 +2640,403 @@
     <t>area-stampa/press-releases/2018/trialsygma</t>
   </si>
   <si>
-    <t>2026-04-05T01:18:29.791Z</t>
+    <t>2026-04-24T09:13:34.881Z</t>
   </si>
   <si>
     <t>Il New England Journal of Medicine ha pubblicato i risultati di due studi di budesonide/formoterolo via turbohaler® come terapia anti-infiammatoria al bisogno per il trattamento dell’asma lieve</t>
   </si>
   <si>
     <t>https://www.astrazeneca.it/area-stampa/press-releases/2018/trialsygma.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-acalabrutinib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-acalabrutinib</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:41:25.869Z</t>
+  </si>
+  <si>
+    <t>Leucemia linfatica cronica: acalabrutinib conferma un miglior profilo di tollerabilità per i pazienti ad alto rischio ricaduti e refrattari ed un beneficio sostenuto a lungo termine anche in prima linea</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_ACALABRUTINIB.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-caspian-esmo-2021.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-caspian-esmo-2021</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:42:01.719Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone a piccole cellule: durvalumab in combinazione con la chemioterapia triplica la sopravvivenza a tre anni nei pazienti con malattia estesa</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_CASPIAN_ESMO_2021.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-destiny-db03-esmo-2021.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-destiny-db03-esmo-2021</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:42:36.478Z</t>
+  </si>
+  <si>
+    <t>Carcinoma mammario metastatico HER2+: Trastuzumab deruxtecan ha ridotto il rischio di progressione della malattia del 72% rispetto a trastuzumab Emtansine (T-DM1)</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_DESTINY_DB03_ESMO_2021.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-osimertinib-ema.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-osimertinib-ema</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:43:10.946Z</t>
+  </si>
+  <si>
+    <t>Tumore del polmone non a piccole cellule: ok dell’Agenzia Europea del Farmaco per osimertinib come terapia adiuvante per i pazienti positivi alla mutazione di EGFR</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_OSIMERTINIB_EMA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-pacific-5yr-asco2021.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-pacific-5yr-asco2021</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:43:46.563Z</t>
+  </si>
+  <si>
+    <t>Carcinoma polmonare non a piccole cellule in stadio III non resecabile: durvalumab mostra un beneficio di sopravvivenza a 5 anni senza precedenti</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_PACIFIC_5YR_ASCO2021.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-risultati-studio-usa.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-risultati-studio-usa</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:44:21.317Z</t>
+  </si>
+  <si>
+    <t>Vaccino AZD1222 per il COVID-19. Raggiunto l'endpoint primario di efficacia nell'analisi ad interim dello studio di Fase III condotto negli Stati Uniti</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_RISULTATI_STUDIO_USA.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-selumetinib.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-selumetinib</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:44:56.344Z</t>
+  </si>
+  <si>
+    <t>Neurofibromatosi di tipo 1 e neurofibromi plessiformi: selumetinib approvato in europa per i pazienti pediatrici</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_SELUMETINIB.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-sicurezza-vaccino.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/comunicato-sicurezza-vaccino</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:45:30.612Z</t>
+  </si>
+  <si>
+    <t>Aggiornamento sulla sicurezza del vaccino AZD1222</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/COMUNICATO_SICUREZZA_VACCINO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/notastampa-vaccino.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2021/notastampa-vaccino</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:46:05.167Z</t>
+  </si>
+  <si>
+    <t>Dichiarazione di AstraZeneca in merito alla segnalazione di eventi avversi segnalati in concomitanza temporale con la somministrazione del vaccino contro Covid-19</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2021/NOTASTAMPA_VACCINO.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali-efficacia-varinati-ba4-ba5.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali-efficacia-varinati-ba4-ba5</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:48:25.317Z</t>
+  </si>
+  <si>
+    <t>Studio dell’Università di Oxford: la combinazione di anticorpi monoclonali a lunga durata d’azione tixagevimab e cilgavimab nella profilassi pre-esposizione al Covid-19 è efficace nel neutralizzare le varianti BA.4 e BA.5 di Omicron</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Anticorpi_monoclonali_efficacia_varinati_BA4_BA5.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali-ema-tackle.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali-ema-tackle</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:47:14.828Z</t>
+  </si>
+  <si>
+    <t>EMA approva la combinazione di anticorpi a lunga durata di azione di AstraZeneca per il trattamento del COVID-19</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Anticorpi_monoclonali_EMA_TACKLE.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali-provent.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali-provent</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:47:51.490Z</t>
+  </si>
+  <si>
+    <t>Pubblicati sul New England Journal of Medicine i risultati dello studio di fase III PROVENT: la combinazione di anticorpi monoclonali a lunga durata d’azione tixagevimab e cilgavimab protegge dal COVID-19 per almeno sei mesi nella popolazione ad alto rischio</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Anticorpi_monoclonali_Provent.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/anticorpi-monoclonali</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:46:40.466Z</t>
+  </si>
+  <si>
+    <t>EMA approva la combinazione di anticorpi a lunga durata d'azione di AstraZeneca, per la prevenzione del COVID-19 nelle persone fragili</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Anticorpi_monoclonali.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/cs-topemployer-2022.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/cs-topemployer-2022</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:49:00.352Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca Italia è Top Employers per l'ottavo anno consecutivo</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/CS_TopEmployer_2022.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/esc-deliver.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/esc-deliver</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:49:36.290Z</t>
+  </si>
+  <si>
+    <t>Dapagliflozin nello studio di Fase III DELIVER ha ridotto significativamente il rischio di morte cardiovascolare o peggioramento dell’insufficienza cardiaca nei pazienti con frazione di eiezione lievemente ridotta o preservata</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/ESC_DELIVER.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/nomina-dorigo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/nomina-dorigo</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:50:59.986Z</t>
+  </si>
+  <si>
+    <t>Alessandra Dorigo nuovo Head of Oncology di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Nomina_Dorigo.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/nomina-longo.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/nomina-longo</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:51:35.133Z</t>
+  </si>
+  <si>
+    <t>Claudio Longo nuovo Presidente e Amministratore Delegato di AstraZeneca Italia</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Nomina_Longo.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/nomine-smt.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/nomine-smt</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:52:11.656Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca Italia fa cresce i propri talenti: tre nuove nomine nel Senior Management Team</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Nomine_SMT.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/npii.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/npii</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:50:25.288Z</t>
+  </si>
+  <si>
+    <t>Per la prima volta in Italia l’evento della Nobel Prize Inspiration Initiative (NPII) in collaborazione con AstraZeneca</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/NPII.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/pan.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/pan</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:52:46.562Z</t>
+  </si>
+  <si>
+    <t>Il ruolo sempre più centrale delle associazioni dei pazienti nella revisione della medicina di territorio</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/PAN.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/sostenibilita.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/sostenibilita</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:53:21.786Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca prosegue con il programma Ambition Zero Carbon con una partnership con Honeywell per sviluppare inalatori respiratori di nuova generazione</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Sostenibilita.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/talkinminds.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/talkinminds</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:53:55.789Z</t>
+  </si>
+  <si>
+    <t>Dalla demografia all’economia: AstraZeneca mette al centro il ruolo delle scienze della vita per garantire la sostenibilità del sistema sanitario</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/TalkinMinds.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/top-employer.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/top-employer</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:55:06.309Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca Italia si conferma Top Employer per il 10° anno consecutivo</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Top_Employer.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/top-employer2025.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/top-employer2025</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:55:41.083Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca Italia si conferma Top Employer nel 2025</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/Top_Employer2025.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/topemployer2023.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2022/topemployer2023</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:54:31.576Z</t>
+  </si>
+  <si>
+    <t>AstraZeneca Italia è Top Employers per il nono anno consecutivo</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2022/TopEmployer2023.html</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2026/amyci-storie-amiloidosi.report.json</t>
+  </si>
+  <si>
+    <t>area-stampa/press-releases/2026/amyci-storie-amiloidosi</t>
+  </si>
+  <si>
+    <t>2026-04-24T07:56:15.769Z</t>
+  </si>
+  <si>
+    <t>AMYCI – Le storie di vita nell’amiloidosi ereditaria da transtiretina diventano un libro</t>
+  </si>
+  <si>
+    <t>https://www.astrazeneca.it/area-stampa/press-releases/2026/amyci-storie-amiloidosi.html</t>
   </si>
 </sst>
 </file>
@@ -3035,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
@@ -8612,6 +9002,838 @@
         <v>877</v>
       </c>
     </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>878</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>12</v>
+      </c>
+      <c r="D175" t="s">
+        <v>12</v>
+      </c>
+      <c r="E175" t="s">
+        <v>879</v>
+      </c>
+      <c r="F175" t="s">
+        <v>14</v>
+      </c>
+      <c r="G175" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" t="s">
+        <v>880</v>
+      </c>
+      <c r="I175" t="s">
+        <v>881</v>
+      </c>
+      <c r="J175" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>883</v>
+      </c>
+      <c r="B176" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>12</v>
+      </c>
+      <c r="D176" t="s">
+        <v>12</v>
+      </c>
+      <c r="E176" t="s">
+        <v>884</v>
+      </c>
+      <c r="F176" t="s">
+        <v>14</v>
+      </c>
+      <c r="G176" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" t="s">
+        <v>885</v>
+      </c>
+      <c r="I176" t="s">
+        <v>886</v>
+      </c>
+      <c r="J176" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>888</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177" t="s">
+        <v>12</v>
+      </c>
+      <c r="E177" t="s">
+        <v>889</v>
+      </c>
+      <c r="F177" t="s">
+        <v>14</v>
+      </c>
+      <c r="G177" t="s">
+        <v>15</v>
+      </c>
+      <c r="H177" t="s">
+        <v>890</v>
+      </c>
+      <c r="I177" t="s">
+        <v>891</v>
+      </c>
+      <c r="J177" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>893</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" t="s">
+        <v>12</v>
+      </c>
+      <c r="E178" t="s">
+        <v>894</v>
+      </c>
+      <c r="F178" t="s">
+        <v>14</v>
+      </c>
+      <c r="G178" t="s">
+        <v>15</v>
+      </c>
+      <c r="H178" t="s">
+        <v>895</v>
+      </c>
+      <c r="I178" t="s">
+        <v>896</v>
+      </c>
+      <c r="J178" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>898</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179" t="s">
+        <v>12</v>
+      </c>
+      <c r="E179" t="s">
+        <v>899</v>
+      </c>
+      <c r="F179" t="s">
+        <v>14</v>
+      </c>
+      <c r="G179" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" t="s">
+        <v>900</v>
+      </c>
+      <c r="I179" t="s">
+        <v>901</v>
+      </c>
+      <c r="J179" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>903</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" t="s">
+        <v>12</v>
+      </c>
+      <c r="E180" t="s">
+        <v>904</v>
+      </c>
+      <c r="F180" t="s">
+        <v>14</v>
+      </c>
+      <c r="G180" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" t="s">
+        <v>905</v>
+      </c>
+      <c r="I180" t="s">
+        <v>906</v>
+      </c>
+      <c r="J180" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>908</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181" t="s">
+        <v>909</v>
+      </c>
+      <c r="F181" t="s">
+        <v>14</v>
+      </c>
+      <c r="G181" t="s">
+        <v>15</v>
+      </c>
+      <c r="H181" t="s">
+        <v>910</v>
+      </c>
+      <c r="I181" t="s">
+        <v>911</v>
+      </c>
+      <c r="J181" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>913</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" t="s">
+        <v>12</v>
+      </c>
+      <c r="E182" t="s">
+        <v>914</v>
+      </c>
+      <c r="F182" t="s">
+        <v>14</v>
+      </c>
+      <c r="G182" t="s">
+        <v>15</v>
+      </c>
+      <c r="H182" t="s">
+        <v>915</v>
+      </c>
+      <c r="I182" t="s">
+        <v>916</v>
+      </c>
+      <c r="J182" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>918</v>
+      </c>
+      <c r="B183" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" t="s">
+        <v>12</v>
+      </c>
+      <c r="D183" t="s">
+        <v>12</v>
+      </c>
+      <c r="E183" t="s">
+        <v>919</v>
+      </c>
+      <c r="F183" t="s">
+        <v>14</v>
+      </c>
+      <c r="G183" t="s">
+        <v>15</v>
+      </c>
+      <c r="H183" t="s">
+        <v>920</v>
+      </c>
+      <c r="I183" t="s">
+        <v>921</v>
+      </c>
+      <c r="J183" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>923</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>12</v>
+      </c>
+      <c r="D184" t="s">
+        <v>12</v>
+      </c>
+      <c r="E184" t="s">
+        <v>924</v>
+      </c>
+      <c r="F184" t="s">
+        <v>14</v>
+      </c>
+      <c r="G184" t="s">
+        <v>15</v>
+      </c>
+      <c r="H184" t="s">
+        <v>925</v>
+      </c>
+      <c r="I184" t="s">
+        <v>926</v>
+      </c>
+      <c r="J184" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>928</v>
+      </c>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" t="s">
+        <v>12</v>
+      </c>
+      <c r="E185" t="s">
+        <v>929</v>
+      </c>
+      <c r="F185" t="s">
+        <v>14</v>
+      </c>
+      <c r="G185" t="s">
+        <v>15</v>
+      </c>
+      <c r="H185" t="s">
+        <v>930</v>
+      </c>
+      <c r="I185" t="s">
+        <v>931</v>
+      </c>
+      <c r="J185" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>933</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>12</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" t="s">
+        <v>934</v>
+      </c>
+      <c r="F186" t="s">
+        <v>14</v>
+      </c>
+      <c r="G186" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" t="s">
+        <v>935</v>
+      </c>
+      <c r="I186" t="s">
+        <v>936</v>
+      </c>
+      <c r="J186" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>938</v>
+      </c>
+      <c r="B187" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" t="s">
+        <v>12</v>
+      </c>
+      <c r="D187" t="s">
+        <v>12</v>
+      </c>
+      <c r="E187" t="s">
+        <v>939</v>
+      </c>
+      <c r="F187" t="s">
+        <v>14</v>
+      </c>
+      <c r="G187" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" t="s">
+        <v>940</v>
+      </c>
+      <c r="I187" t="s">
+        <v>941</v>
+      </c>
+      <c r="J187" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>943</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>12</v>
+      </c>
+      <c r="D188" t="s">
+        <v>12</v>
+      </c>
+      <c r="E188" t="s">
+        <v>944</v>
+      </c>
+      <c r="F188" t="s">
+        <v>14</v>
+      </c>
+      <c r="G188" t="s">
+        <v>15</v>
+      </c>
+      <c r="H188" t="s">
+        <v>945</v>
+      </c>
+      <c r="I188" t="s">
+        <v>946</v>
+      </c>
+      <c r="J188" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>948</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189" t="s">
+        <v>12</v>
+      </c>
+      <c r="E189" t="s">
+        <v>949</v>
+      </c>
+      <c r="F189" t="s">
+        <v>14</v>
+      </c>
+      <c r="G189" t="s">
+        <v>15</v>
+      </c>
+      <c r="H189" t="s">
+        <v>950</v>
+      </c>
+      <c r="I189" t="s">
+        <v>951</v>
+      </c>
+      <c r="J189" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>953</v>
+      </c>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>12</v>
+      </c>
+      <c r="D190" t="s">
+        <v>12</v>
+      </c>
+      <c r="E190" t="s">
+        <v>954</v>
+      </c>
+      <c r="F190" t="s">
+        <v>14</v>
+      </c>
+      <c r="G190" t="s">
+        <v>15</v>
+      </c>
+      <c r="H190" t="s">
+        <v>955</v>
+      </c>
+      <c r="I190" t="s">
+        <v>956</v>
+      </c>
+      <c r="J190" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>958</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" t="s">
+        <v>12</v>
+      </c>
+      <c r="D191" t="s">
+        <v>12</v>
+      </c>
+      <c r="E191" t="s">
+        <v>959</v>
+      </c>
+      <c r="F191" t="s">
+        <v>14</v>
+      </c>
+      <c r="G191" t="s">
+        <v>15</v>
+      </c>
+      <c r="H191" t="s">
+        <v>960</v>
+      </c>
+      <c r="I191" t="s">
+        <v>961</v>
+      </c>
+      <c r="J191" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>963</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" t="s">
+        <v>12</v>
+      </c>
+      <c r="E192" t="s">
+        <v>964</v>
+      </c>
+      <c r="F192" t="s">
+        <v>14</v>
+      </c>
+      <c r="G192" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" t="s">
+        <v>965</v>
+      </c>
+      <c r="I192" t="s">
+        <v>966</v>
+      </c>
+      <c r="J192" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>968</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>12</v>
+      </c>
+      <c r="D193" t="s">
+        <v>12</v>
+      </c>
+      <c r="E193" t="s">
+        <v>969</v>
+      </c>
+      <c r="F193" t="s">
+        <v>14</v>
+      </c>
+      <c r="G193" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" t="s">
+        <v>970</v>
+      </c>
+      <c r="I193" t="s">
+        <v>971</v>
+      </c>
+      <c r="J193" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>973</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" t="s">
+        <v>12</v>
+      </c>
+      <c r="D194" t="s">
+        <v>12</v>
+      </c>
+      <c r="E194" t="s">
+        <v>974</v>
+      </c>
+      <c r="F194" t="s">
+        <v>14</v>
+      </c>
+      <c r="G194" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" t="s">
+        <v>975</v>
+      </c>
+      <c r="I194" t="s">
+        <v>976</v>
+      </c>
+      <c r="J194" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>978</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>12</v>
+      </c>
+      <c r="D195" t="s">
+        <v>12</v>
+      </c>
+      <c r="E195" t="s">
+        <v>979</v>
+      </c>
+      <c r="F195" t="s">
+        <v>14</v>
+      </c>
+      <c r="G195" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" t="s">
+        <v>980</v>
+      </c>
+      <c r="I195" t="s">
+        <v>981</v>
+      </c>
+      <c r="J195" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>983</v>
+      </c>
+      <c r="B196" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" t="s">
+        <v>12</v>
+      </c>
+      <c r="D196" t="s">
+        <v>12</v>
+      </c>
+      <c r="E196" t="s">
+        <v>984</v>
+      </c>
+      <c r="F196" t="s">
+        <v>14</v>
+      </c>
+      <c r="G196" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" t="s">
+        <v>985</v>
+      </c>
+      <c r="I196" t="s">
+        <v>986</v>
+      </c>
+      <c r="J196" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>988</v>
+      </c>
+      <c r="B197" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" t="s">
+        <v>12</v>
+      </c>
+      <c r="D197" t="s">
+        <v>12</v>
+      </c>
+      <c r="E197" t="s">
+        <v>989</v>
+      </c>
+      <c r="F197" t="s">
+        <v>14</v>
+      </c>
+      <c r="G197" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" t="s">
+        <v>990</v>
+      </c>
+      <c r="I197" t="s">
+        <v>991</v>
+      </c>
+      <c r="J197" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>993</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>12</v>
+      </c>
+      <c r="D198" t="s">
+        <v>12</v>
+      </c>
+      <c r="E198" t="s">
+        <v>994</v>
+      </c>
+      <c r="F198" t="s">
+        <v>14</v>
+      </c>
+      <c r="G198" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" t="s">
+        <v>995</v>
+      </c>
+      <c r="I198" t="s">
+        <v>996</v>
+      </c>
+      <c r="J198" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>998</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" t="s">
+        <v>12</v>
+      </c>
+      <c r="D199" t="s">
+        <v>12</v>
+      </c>
+      <c r="E199" t="s">
+        <v>999</v>
+      </c>
+      <c r="F199" t="s">
+        <v>14</v>
+      </c>
+      <c r="G199" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I199" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J199" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" t="s">
+        <v>12</v>
+      </c>
+      <c r="D200" t="s">
+        <v>12</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F200" t="s">
+        <v>14</v>
+      </c>
+      <c r="G200" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I200" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J200" t="s">
+        <v>1007</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
